--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
@@ -575,46 +575,46 @@
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.50656167979002</v>
+        <v>15.45747858305265</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.105592804704706</v>
+        <v>-2.098041474812185</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.504681409993168</v>
+        <v>9.475028086531779</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.63139044330461</v>
+        <v>1.626979324619306</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.91511677773002</v>
+        <v>-6.89214559736962</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.62415886614551</v>
+        <v>-10.5889234539213</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.705769532391081</v>
+        <v>-6.683173299425128</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.845321276596053</v>
+        <v>4.830751661851366</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.785223020507466</v>
+        <v>4.771009458703112</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.083445850989008</v>
+        <v>-4.069294803248411</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.730158575223825</v>
+        <v>3.719029442504457</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.256676742887144</v>
+        <v>-4.241717756185693</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6675632005594636</v>
+        <v>-0.6639996287963115</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4174496444165925</v>
+        <v>-0.4145524174245949</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.8805350944049906</v>
+        <v>-0.8773348483639438</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.39922870327637</v>
+        <v>-15.34860424033126</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-12.57074853930533</v>
+        <v>-12.52946203103701</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12.44361002092872</v>
+        <v>-12.40258902042185</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.388338077482423</v>
+        <v>6.368629365496716</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.917317870518005</v>
+        <v>9.88664925129352</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.373637799592998</v>
+        <v>3.363969759495646</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.369433430436509</v>
+        <v>9.340038018466309</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.310474836389751</v>
+        <v>9.281436751198505</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.227575528060157</v>
+        <v>5.211828311439952</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.72535734722968</v>
+        <v>14.67853432702771</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.52825362118602</v>
+        <v>11.49240047673949</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.3449240451392</v>
+        <v>14.30001353083772</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.36252098950955</v>
+        <v>11.32738306644343</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.966021139249484</v>
+        <v>6.943678696630307</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.35569514836255</v>
+        <v>5.339476061351263</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.37003763701303</v>
+        <v>10.33719045953103</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.20762298178101</v>
+        <v>13.16566365581379</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.850320634302861</v>
+        <v>1.845079685012685</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.148399173149663</v>
+        <v>2.142551250776791</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.063982692582421</v>
+        <v>2.058422077743508</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.01159490529443</v>
+        <v>6.98938970984171</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.535799607398957</v>
+        <v>1.531628821626249</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.683934059826683</v>
+        <v>0.6827405517045761</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.939766495192345</v>
+        <v>-4.923236279617875</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5131871157064438</v>
+        <v>0.5126558911448527</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.09172572176046856</v>
+        <v>0.09254611416351821</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3419903125774866</v>
+        <v>0.3422043393333851</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.649418822647974</v>
+        <v>4.634212542653046</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.252363707006729</v>
+        <v>1.249337527513823</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.715654407337993</v>
+        <v>-2.705982061006893</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9880972111318087</v>
+        <v>0.9855758128041927</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.125749657913403</v>
+        <v>-3.114650188390399</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.040934482424646</v>
+        <v>-1.03636818215945</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.703047289217132</v>
+        <v>-4.686349249797736</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.960892243059511</v>
+        <v>-6.937391851911876</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-15.97082808233541</v>
+        <v>-15.91717288773352</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-11.4577584757462</v>
+        <v>-11.41880665256265</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-17.03649284810786</v>
+        <v>-16.97954655907124</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-17.00689559624921</v>
+        <v>-16.94947017245963</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-15.6416735296285</v>
+        <v>-15.58877614899311</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-13.60377141267044</v>
+        <v>-13.55740956028175</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.038892865664181</v>
+        <v>-7.124836126908029</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.137246615021169</v>
+        <v>-7.228509721065656</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.186906487625826</v>
+        <v>-5.253393533595371</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.028594958424748</v>
+        <v>-2.056037435039805</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.558967333782533</v>
+        <v>-2.593648334332642</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.815468544757245</v>
+        <v>-6.903213088028195</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.900098992474526</v>
+        <v>-6.989572457528737</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.847659386072131</v>
+        <v>-5.922149324445613</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.870496783524835</v>
+        <v>-2.911432640625378</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6736777876960574</v>
+        <v>-0.6878180156357416</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.160473530541339</v>
+        <v>2.18176351272718</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.754349859065712</v>
+        <v>6.829666617393102</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.782163394791489</v>
+        <v>1.796946992065429</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.010147378056701</v>
+        <v>-1.029937032809912</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>72</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.485203221386001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.840062384675676</v>
+        <v>2.832503903805069</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.890413576058833</v>
+        <v>-5.870685007278261</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2032017948152003</v>
+        <v>-0.201756068903947</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.132215545442762</v>
+        <v>-2.124437141501943</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4449174889415985</v>
+        <v>-0.4419853756775538</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8606372434707978</v>
+        <v>0.8596239881741639</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.389076403698006</v>
+        <v>-2.380415841894298</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.114575007322294</v>
+        <v>3.106405646044919</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.912077116260811</v>
+        <v>-1.904434899545038</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.509882997499183</v>
+        <v>-3.497538358598675</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.084145238587311</v>
+        <v>-2.075993918789599</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.672308085063079</v>
+        <v>1.668764265320341</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5295564702854421</v>
+        <v>0.5298920270204732</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.256561679790025</v>
+        <v>1.267174073804277</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.106228071543619</v>
+        <v>-4.149808928811034</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.25088075356058</v>
+        <v>-3.28672027434007</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.870777050963561</v>
+        <v>-1.891374256661017</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.414343083923143</v>
+        <v>-7.48953016382346</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-9.621515428084393</v>
+        <v>-9.719244446857914</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.954082803435675</v>
+        <v>-6.016739653944882</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.423554551074353</v>
+        <v>-6.489435925689996</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.739036129278951</v>
+        <v>-7.818449224540331</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-6.629416157911535</v>
+        <v>-6.698725979546531</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.076754618950012</v>
+        <v>-3.110946678383797</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.295948151730016</v>
+        <v>-4.342645747375173</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.80680460178155</v>
+        <v>2.828776249131067</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.959097753313699</v>
+        <v>-1.984172670589736</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.419364246136112</v>
+        <v>-3.477363505418431</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.106291545728446</v>
+        <v>-4.181547250099243</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-10.05837789072407</v>
+        <v>-10.23138288231917</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.643058552406785</v>
+        <v>-6.756522807118131</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.103145520196726</v>
+        <v>-8.244220501901083</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.882418205688573</v>
+        <v>-7.006465036713351</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.895876591755922</v>
+        <v>-8.035767012677773</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.508345803430025</v>
+        <v>-6.623492655272173</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.0776673151563898</v>
+        <v>-0.08974090038932303</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.006454903475926699</v>
+        <v>-0.004911596365708704</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.52593969517946</v>
+        <v>-1.55966819118273</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5632506738047312</v>
+        <v>-0.582958915305035</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.907604301726884</v>
+        <v>-1.946616752264951</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.7309234629271799</v>
+        <v>-0.7541750589336047</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>103</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.06625385419078356</v>
+        <v>-0.06546532960246765</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.004173275510894</v>
+        <v>8.982671445884904</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.073533827339311</v>
+        <v>-2.065994945048594</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.798902101451858</v>
+        <v>-6.780090947030025</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5398815868231424</v>
+        <v>-0.5364395214200925</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7290139537369384</v>
+        <v>0.7295692146956725</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6441372260720541</v>
+        <v>0.6448754451737528</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.740336245805906</v>
+        <v>-2.731341985552781</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.005470830555943</v>
+        <v>3.996930360899057</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.208735947090979</v>
+        <v>1.207488665866023</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.003839400960366</v>
+        <v>1.002806952455067</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.798666474616844</v>
+        <v>-4.7845775975807</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.274967617730063</v>
+        <v>-3.265121482216195</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.91967598898546</v>
+        <v>-6.899989310628484</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>107</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.764466357592724</v>
+        <v>-5.748514407512786</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1005083740616683</v>
+        <v>0.1012928986624146</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.229493340787734</v>
+        <v>-1.223726695190116</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.968849028827641</v>
+        <v>-2.959032903944397</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.98978700719442</v>
+        <v>-10.9584133230118</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-10.69567108352202</v>
+        <v>-10.66477725193644</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.041197727883606</v>
+        <v>-7.020028314971761</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.767474429835083</v>
+        <v>-3.755198991183128</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-10.38310865985778</v>
+        <v>-10.35401172403729</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.681312474569978</v>
+        <v>-4.66701348207301</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.88621790070664</v>
+        <v>-4.871690755481268</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.70168054209455</v>
+        <v>1.699399109973051</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.339629213689967</v>
+        <v>-4.326349643805351</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.217377128343188</v>
+        <v>-2.208944940789095</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>127</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.049868766404018</v>
+        <v>1.048185609381598</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.739140801322158</v>
+        <v>5.724443356208042</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.981036876222959</v>
+        <v>2.975613877949513</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7484520858286743</v>
+        <v>0.7487278748855104</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2094481385803562</v>
+        <v>0.2122083279022959</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.294883244344518</v>
+        <v>1.294948590822877</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.998561505918261</v>
+        <v>1.996337106679569</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.685628548213188</v>
+        <v>4.67548957346753</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.414631886138643</v>
+        <v>5.402280266560858</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.140741085409275</v>
+        <v>6.126242613792563</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.513526301846071</v>
+        <v>7.494924743507696</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.815387555164158</v>
+        <v>2.80987366185613</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.39469014665373</v>
+        <v>2.39036363727044</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.224083014138721</v>
+        <v>4.215368842417924</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>154</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.350717523945868</v>
+        <v>3.342228259615915</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.337876737415044</v>
+        <v>4.325904676137199</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.891321894880747</v>
+        <v>5.87699258951136</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.423406436032707</v>
+        <v>3.4159710771373</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.834514665293874</v>
+        <v>4.824148252578695</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.683170147030225</v>
+        <v>9.658982209523046</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.30085100451614</v>
+        <v>8.280199336102534</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.185295989982301</v>
+        <v>7.167012394773863</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.475811822862312</v>
+        <v>6.45927594090243</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.672390150605708</v>
+        <v>3.663721077410777</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.166367511852336</v>
+        <v>2.161550462259441</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.200832773550552</v>
+        <v>2.196598311160223</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.081945758294644</v>
+        <v>3.075241019591992</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.07646004585566146</v>
+        <v>0.07895407608189231</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>161</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.543828760535227</v>
+        <v>1.539943996580305</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.038394049324488</v>
+        <v>-5.023048171673928</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1583238189094942</v>
+        <v>0.1599495292950905</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.637909566644126</v>
+        <v>4.625976523496846</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.343292846795698</v>
+        <v>5.3302682085165</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.399155923435139</v>
+        <v>4.388501339942621</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.315627082374299</v>
+        <v>4.304925173278932</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.849276731077389</v>
+        <v>3.839215718329307</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.922275718133726</v>
+        <v>1.917862175084906</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7968364448232137</v>
+        <v>-0.7928005768787827</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.00178655131527</v>
+        <v>-0.9974555101096172</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.767180489173235</v>
+        <v>2.760766770566619</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4781204990017756</v>
+        <v>0.4786412549254564</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1045120146028182</v>
+        <v>0.1071867130101793</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.270088066402749</v>
+        <v>-4.255478093267548</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2096877527665058</v>
+        <v>0.2098778889430193</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8301084136482402</v>
+        <v>0.8297500800847502</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.594105514761196</v>
+        <v>-2.583955730644163</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.658234278413978</v>
+        <v>-4.640267295915066</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.329659488755198</v>
+        <v>-2.319709497876275</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.432183441097237</v>
+        <v>-3.418956878422293</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.426856167426962</v>
+        <v>-5.407910878968963</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.420374803051175</v>
+        <v>-1.414438380131188</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.781520851478504</v>
+        <v>-2.770474453256419</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.530109299947618</v>
+        <v>-5.510416814482824</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.444522514883317</v>
+        <v>-2.434738261167695</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.358315469965589</v>
+        <v>-2.348457620962328</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.147205348998384</v>
+        <v>-4.130288458033625</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6262184031975195</v>
+        <v>-0.6273305338580286</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.501787687424851</v>
+        <v>-4.506418082873751</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.893189787241681</v>
+        <v>-4.898627172331032</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.933513302063787</v>
+        <v>-3.938040484707308</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.639693135142416</v>
+        <v>-3.64441937565725</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.761465455991448</v>
+        <v>-3.766018719009189</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.77073353546642</v>
+        <v>-1.773328549600706</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2555029194245009</v>
+        <v>0.2549892398255196</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6376665398754824</v>
+        <v>-0.6387953544204947</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.901036736542807</v>
+        <v>-1.90369587845106</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.768220017734997</v>
+        <v>-3.772774018380467</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.07233527780172</v>
+        <v>-2.075086035681927</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.66080227357152</v>
+        <v>-1.663260885600124</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2532262351877961</v>
+        <v>0.252114249241977</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.529637415232706</v>
+        <v>-4.589234625202778</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.688722340413946</v>
+        <v>-5.762856469729876</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.368658920313813</v>
+        <v>-3.422006710736774</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.405826602185847</v>
+        <v>-6.493459893658226</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.878147001625763</v>
+        <v>-4.95412692085138</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.133404425369321</v>
+        <v>-4.197118846060363</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.323902332217159</v>
+        <v>-5.398805299810796</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.339872995453135</v>
+        <v>-5.411202632540004</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.763879219093106</v>
+        <v>-6.849367295758768</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.244560515433676</v>
+        <v>-6.32942888648396</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.804850398514581</v>
+        <v>-7.910901434237701</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.964111805656408</v>
+        <v>-6.044958077700336</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.930495718352638</v>
+        <v>-6.011894505757844</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.603206210274699</v>
+        <v>-3.662258839442956</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>258</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9949337728133614</v>
+        <v>0.9952605165584245</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2290429409262629</v>
+        <v>-0.2251644178455194</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1512821509266686</v>
+        <v>0.1550783645143738</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1060616156905496</v>
+        <v>-0.1010981038379626</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.293501665361404</v>
+        <v>1.296060742326553</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.978571792309772</v>
+        <v>1.9784153422708</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4328657661224256</v>
+        <v>-0.4274099871062518</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.841143592889729</v>
+        <v>-2.830640873727482</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.739710853931086</v>
+        <v>-1.732112253600313</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9017528282199905</v>
+        <v>0.9039901382910642</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.860539806751092</v>
+        <v>1.861527774865223</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.211004839502706</v>
+        <v>-1.203823101166115</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.64012541429269</v>
+        <v>2.638051831694376</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1700902043607257</v>
+        <v>0.1745948693970121</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.98601373458451</v>
+        <v>2.988098683671467</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.114166149017549</v>
+        <v>4.117070893374624</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.376831688996376</v>
+        <v>3.378513603850557</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.507084821603797</v>
+        <v>3.508599727002945</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.653595113380945</v>
+        <v>3.654939196323838</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.553573975103674</v>
+        <v>1.553173946376354</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.524673751706608</v>
+        <v>3.526323106793264</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.057899413009551</v>
+        <v>3.059127527818255</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.968644791626652</v>
+        <v>1.968899742612749</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.832018624478295</v>
+        <v>2.833043018687775</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.341528777147168</v>
+        <v>4.343825248632058</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.974915111282748</v>
+        <v>1.974794871028458</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.098150231471728</v>
+        <v>2.098612848237337</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.377967837979831</v>
+        <v>3.379262015565168</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1555683023066194</v>
+        <v>0.1547299236716384</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7937536550285458</v>
+        <v>-0.7961100141976729</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.791510088705998</v>
+        <v>1.791693688943376</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.246266532571774</v>
+        <v>3.247869756073264</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2722871328315151</v>
+        <v>-0.2754162991223197</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3075499279390215</v>
+        <v>-0.3103510418080404</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.38037934643711</v>
+        <v>-2.385559038833442</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.002364669869436</v>
+        <v>-1.005806722394986</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.587335826635638</v>
+        <v>1.587189944890255</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4073954496291563</v>
+        <v>0.4057097050163208</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.122928444467512</v>
+        <v>-1.126743216870956</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9003146711693546</v>
+        <v>0.8988380041011936</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.842730533154977</v>
+        <v>-1.846998002192578</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5973454631577368</v>
+        <v>-0.6005989290525093</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.0344219267673509</v>
+        <v>-0.03689020142356725</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8130208537110164</v>
+        <v>0.811298608136255</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.860536377475697</v>
+        <v>-2.871430066070573</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.959791441589502</v>
+        <v>-3.973511165998637</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.649328326944833</v>
+        <v>1.646524477869079</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.770760057207724</v>
+        <v>1.769122648155033</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.001074219423877</v>
+        <v>-2.012540245697238</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.238179809162311</v>
+        <v>-1.246987820994526</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.534655188153323</v>
+        <v>-2.545045742057496</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.740204435131133</v>
+        <v>-1.749468587117327</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7119231423354719</v>
+        <v>-0.7200469947861308</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2705563332101946</v>
+        <v>-0.2769409494555788</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6897962536726823</v>
+        <v>-0.6971955604004805</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4400749213963948</v>
+        <v>-0.447474228124193</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.401758186340238</v>
+        <v>3.409176702888992</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.410271909620576</v>
+        <v>4.419463781607952</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.452084425731307</v>
+        <v>4.4585398795057</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.525568999386849</v>
+        <v>1.521232772580412</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.480597565974122</v>
+        <v>4.485436100902774</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.524764394519423</v>
+        <v>6.53796862067977</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.566668231832338</v>
+        <v>5.573030801379822</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.536166055758265</v>
+        <v>5.544270204561379</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.727673889149834</v>
+        <v>5.738140671300272</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.249111438221519</v>
+        <v>9.27056974829091</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.920643948257393</v>
+        <v>9.942794580250094</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.39750077377059</v>
+        <v>10.42264752791063</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.044723150138232</v>
+        <v>6.055024495913138</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.545911387764122</v>
+        <v>4.550359863277194</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>218</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.552433239423081</v>
+        <v>2.549907489408049</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.02342843379822312</v>
+        <v>0.0247508425323133</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.28887146545889</v>
+        <v>-1.284391235868462</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6762440524697055</v>
+        <v>0.6795171407540224</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.073186336914389</v>
+        <v>-3.065488119403604</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.234459995529001</v>
+        <v>-3.227944219161174</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.025615731149905</v>
+        <v>-1.019953060416498</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.034083533601155</v>
+        <v>-1.029309435403157</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6363678234531847</v>
+        <v>-0.6330345681048186</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.862639797471907</v>
+        <v>-2.857055027252997</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.067393121789486</v>
+        <v>-3.060979946099287</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.497872088718616</v>
+        <v>-3.491725560774285</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.001544923899203</v>
+        <v>-2.994548979058663</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9150617628387749</v>
+        <v>-0.9099652614613234</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.538024307471154</v>
+        <v>-1.548588777229632</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.149597920435411</v>
+        <v>-3.178135071717961</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.907523951872733</v>
+        <v>-2.945671608926268</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.140328144106029</v>
+        <v>-2.17867204517983</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.04180668401893</v>
+        <v>-2.082914355045041</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4704793959848033</v>
+        <v>-0.4931510315500418</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.814213638335275</v>
+        <v>5.822957399683318</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.073144889235337</v>
+        <v>4.076290244782619</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.012145003053035</v>
+        <v>4.021281252441675</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.251191792547402</v>
+        <v>1.242944092472797</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.046438468229788</v>
+        <v>1.033055716291194</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.091584934952195</v>
+        <v>2.089314194577348</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.319342858494153</v>
+        <v>2.310085224658053</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.56906419077044</v>
+        <v>2.55980655693434</v>
       </c>
     </row>
     <row r="29">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01779</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.2039623664011074</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01667</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4040~4053</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4040</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1095717957535101</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01554</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4009~4022</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4009</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1172031516945538</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01442</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3972~3985</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3972</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.05361312270094487</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.01329</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3916~3929</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3916</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.01189085266098289</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01216</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3851~3863</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3851</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.1081666500204079</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01104</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3779~3791</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3779</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.1575772429659636</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.009912</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3700~3711</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3700</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.1338858511723942</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.008786</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3594~3603</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3594</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2403945968036254</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.00766</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3491~3500</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3491</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.2494188226471721</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.006534</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3384~3393</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3384</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.4390697847119185</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.005408</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3257~3266</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3257</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.4153185689510792</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.004282</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3103~3112</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3103</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.2700578237488926</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.003156</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2942~2951</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2942</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.2005637129991129</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.002031</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2745~2754</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2745</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5203597916273566</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; -0.0009046</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2505~2513</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2505</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.6303181461648748</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.0002213</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2287~2292</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2287</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.127853128306612</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.001347</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2029~2034</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2029</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.144713105552071</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.002473</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1738~1742</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1738</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.8360679943709712</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.003599</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1437~1440</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1437</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.9787839020122462</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.004725</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1194~1196</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1194</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.185491445676313</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.005851</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>966~967</t>
-        </is>
+      <c r="B27" t="n">
+        <v>966</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.6606464781354262</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.006977</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>748~749</t>
-        </is>
+      <c r="B28" t="n">
+        <v>748</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.1100329748500997</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.008103</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>592~592</t>
-        </is>
+      <c r="B29" t="n">
+        <v>592</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.5471022203305651</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.009229</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>445~445</t>
-        </is>
+      <c r="B30" t="n">
+        <v>445</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.5402695449585693</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01035</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>336~336</t>
-        </is>
+      <c r="B31" t="n">
+        <v>336</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.375609298837638</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01148</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>237~237</t>
-        </is>
+      <c r="B32" t="n">
+        <v>237</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.202764211435593</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.01261</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>163~163</t>
-        </is>
+      <c r="B33" t="n">
+        <v>163</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4.561776403716408</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01373</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>106~106</t>
-        </is>
+      <c r="B34" t="n">
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>3.166939038280589</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.01486</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>4.649418822647164</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01779</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-8.445819272590931</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01667</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>109~109</t>
-        </is>
+      <c r="B7" t="n">
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-2.952153916540247</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01554</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>140~140</t>
-        </is>
+      <c r="B8" t="n">
+        <v>140</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01442</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>177~177</t>
-        </is>
+      <c r="B9" t="n">
+        <v>177</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.5160371902664735</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.01329</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>233~233</t>
-        </is>
+      <c r="B10" t="n">
+        <v>233</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.7254457999616974</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01216</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>298~299</t>
-        </is>
+      <c r="B11" t="n">
+        <v>298</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.9884215978019526</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01104</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>370~371</t>
-        </is>
+      <c r="B12" t="n">
+        <v>370</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.280500314819136</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.009912</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>449~451</t>
-        </is>
+      <c r="B13" t="n">
+        <v>449</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.8304671450436842</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.008786</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>555~559</t>
-        </is>
+      <c r="B14" t="n">
+        <v>555</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.330647622535551</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.00766</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>658~662</t>
-        </is>
+      <c r="B15" t="n">
+        <v>658</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.133921703895773</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.006534</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>765~769</t>
-        </is>
+      <c r="B16" t="n">
+        <v>765</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.778223755840656</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.005408</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>892~896</t>
-        </is>
+      <c r="B17" t="n">
+        <v>892</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.377366891638545</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.004282</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1046~1050</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1046</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6839145106861722</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.003156</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1207~1211</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1207</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3877405497723245</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.002031</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1404~1408</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1404</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.9309383202099752</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; -0.0009046</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1644~1649</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1644</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.8864037538060856</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.0002213</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1862~1870</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1862</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.316967731974685</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.001347</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2120~2128</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2120</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.036671402916745</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.002473</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2411~2420</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2411</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5512895598794003</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.003599</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2712~2722</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2712</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.4728652122011567</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.004725</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2955~2966</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2955</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.4367963782005333</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.005851</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3183~3195</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3183</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.161669932103564</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.006977</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3401~3413</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3401</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.0116891336429461</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.008103</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3557~3570</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3557</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.05646353029400331</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.009229</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3704~3717</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3704</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.03177568905581296</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01035</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3813~3826</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3813</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.08883821566215033</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01148</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3912~3925</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3912</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1622281291271719</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.01261</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3986~3999</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3986</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1553537990796983</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01373</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4043~4056</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4043</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.05260991784310676</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.01486</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4065</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.06577770226000013</v>

--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.45747858305265</v>
+        <v>15.46997155194513</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.098041474812185</v>
+        <v>-2.085172847734668</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.475028086531779</v>
+        <v>9.488004948092154</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.626979324619306</v>
+        <v>1.639926221914493</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.89214559736962</v>
+        <v>-6.879068797206237</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.5889234539213</v>
+        <v>-10.57591257289909</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.683173299425128</v>
+        <v>-6.670133416472865</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.830751661851366</v>
+        <v>4.843914138229358</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.771009458703112</v>
+        <v>4.784192677796533</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.069294803248411</v>
+        <v>-4.0559044558631</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.719029442504457</v>
+        <v>3.732477063412929</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.241717756185693</v>
+        <v>-4.228272925651375</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6639996287963115</v>
+        <v>-0.6504471242208041</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="7">
@@ -627,98 +627,98 @@
         <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.8773348483639438</v>
+        <v>-0.8648552837231449</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.34860424033126</v>
+        <v>-15.33574607223404</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-12.52946203103701</v>
+        <v>-12.51650051916805</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12.40258902042185</v>
+        <v>-12.38965126578853</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.368629365496716</v>
+        <v>6.381713043834239</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.88664925129352</v>
+        <v>9.899669779765645</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.363969759495646</v>
+        <v>3.377013599698202</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.340038018466309</v>
+        <v>9.3532019402763</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.281436751198505</v>
+        <v>9.294621173930665</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.211828311439952</v>
+        <v>5.225220744471351</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.67853432702771</v>
+        <v>14.69198386554994</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.49240047673949</v>
+        <v>11.50584715163729</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.30001353083772</v>
+        <v>14.31356691560296</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.32738306644343</v>
+        <v>11.31695343074674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01498</t>
+          <t>X ≈ -0.01497</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.943678696630307</v>
+        <v>6.956163940494889</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.339476061351263</v>
+        <v>5.352348831733472</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.33719045953103</v>
+        <v>10.35016693785663</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.16566365581379</v>
+        <v>13.17861672971713</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.845079685012685</v>
+        <v>1.858160384770095</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.142551250776791</v>
+        <v>2.155567560388967</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.058422077743508</v>
+        <v>2.071464979292649</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.98938970984171</v>
+        <v>7.002552505609572</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.531628821626249</v>
+        <v>1.544810595327746</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6827405517045761</v>
+        <v>0.6961316416876926</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.923236279617875</v>
+        <v>-4.909790550785409</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5126558911448527</v>
+        <v>0.5261011029306033</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.09254611416351821</v>
+        <v>0.1060985681929481</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3422043393333851</v>
+        <v>0.331774703635233</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.634212542653046</v>
+        <v>4.646695094043828</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.249337527513823</v>
+        <v>1.262206321639795</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.705982061006893</v>
+        <v>-2.693015467810447</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9855758128041927</v>
+        <v>0.9985205441457978</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.114650188390399</v>
+        <v>-3.10157308321488</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.03636818215945</v>
+        <v>-1.023354135302569</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.686349249797736</v>
+        <v>-4.673309956106706</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.937391851911876</v>
+        <v>-6.924234865153792</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-15.91717288773352</v>
+        <v>-15.90399718708998</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-11.41880665256265</v>
+        <v>-11.40541904585182</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.97954655907124</v>
+        <v>-16.96610348389203</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-16.94947017245963</v>
+        <v>-16.93602740378761</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-15.58877614899311</v>
+        <v>-15.57522480267463</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-13.56783919597908</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.124836126908029</v>
+        <v>-7.11215623628464</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.228509721065656</v>
+        <v>-7.215432423015663</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.253393533595371</v>
+        <v>-6.081751490903258</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.056037435039805</v>
+        <v>-2.043095811165053</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.593648334332642</v>
+        <v>-2.580572032430481</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.903213088028195</v>
+        <v>-6.890203125823561</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.989572457528737</v>
+        <v>-6.976535167292468</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.922149324445613</v>
+        <v>-5.908992769450123</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.911432640625378</v>
+        <v>-2.898253452778782</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6878180156357416</v>
+        <v>-0.6744281657791475</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.18176351272718</v>
+        <v>2.19520990662334</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.829666617393102</v>
+        <v>6.843112219502558</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.796946992065429</v>
+        <v>1.81049932931154</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.029937032809912</v>
+        <v>-1.040366668508767</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>72</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.485203221386001</v>
+        <v>-2.472726183323992</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.832503903805069</v>
+        <v>2.84537456154667</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.870685007278261</v>
+        <v>-5.859321923258513</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.201756068903947</v>
+        <v>-0.1888145629840636</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.124437141501943</v>
+        <v>-2.11136185637455</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4419853756775538</v>
+        <v>-0.4289731380523136</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8596239881741639</v>
+        <v>0.8726639410278878</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.380415841894298</v>
+        <v>-2.367258778491795</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.106405646044919</v>
+        <v>3.11958618771979</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.904434899545038</v>
+        <v>-1.891045954787231</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.497538358598675</v>
+        <v>-3.484093538078383</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.075993918789599</v>
+        <v>-2.062549774093057</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.668764265320341</v>
+        <v>1.682316462246987</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5298920270204732</v>
+        <v>0.5194623913223211</v>
       </c>
     </row>
     <row r="12">
@@ -887,306 +887,306 @@
         <v>79</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.267174073804277</v>
+        <v>1.279831342233869</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.149808928811034</v>
+        <v>-4.136759659773048</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.28672027434007</v>
+        <v>-3.274725916381307</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.891374256661017</v>
+        <v>-1.878249472279272</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.48953016382346</v>
+        <v>-7.476271131043916</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-9.719244446857914</v>
+        <v>-9.70605041870418</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.016739653944882</v>
+        <v>-6.00351556118779</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.489435925689996</v>
+        <v>-6.476091712653336</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.818449224540331</v>
+        <v>-7.805082693705288</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-6.698725979546531</v>
+        <v>-7.403252548696415</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.110946678383797</v>
+        <v>-3.097502315733408</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.342645747375173</v>
+        <v>-4.329202280617828</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.828776249131067</v>
+        <v>2.842328376988064</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.984172670589736</v>
+        <v>-1.994602306287312</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.009349</t>
+          <t>X ≈ -0.009348</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>106</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.477363505418431</v>
+        <v>-3.464612295419926</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.181547250099243</v>
+        <v>-4.168395975025732</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-10.23138288231917</v>
+        <v>-10.22137294998601</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.756522807118131</v>
+        <v>-7.260086426589652</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.244220501901083</v>
+        <v>-8.231002740594214</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.006465036713351</v>
+        <v>-6.993310051517334</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-8.035767012677773</v>
+        <v>-8.022584154693327</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.623492655272173</v>
+        <v>-6.610188916443093</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.08974090038932303</v>
+        <v>-0.07641273119077852</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.004911596365708704</v>
+        <v>0.008296614061528373</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.55966819118273</v>
+        <v>-2.082387448435831</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.582958915305035</v>
+        <v>-0.5695153583930121</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.946616752264951</v>
+        <v>-1.933065186608061</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.7541750589336047</v>
+        <v>-0.7646046946317568</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008223</t>
+          <t>X ≈ -0.008222</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>103</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.06546532960246765</v>
+        <v>-0.05298087962543008</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.982671445884904</v>
+        <v>8.995551984956101</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.065994945048594</v>
+        <v>-2.053825467218672</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.780090947030025</v>
+        <v>-6.769201932900678</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5364395214200925</v>
+        <v>-0.5233604220169923</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7295692146956725</v>
+        <v>0.7425855423641465</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6448754451737528</v>
+        <v>0.6579194892268561</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.731341985552781</v>
+        <v>-2.718179897309376</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.996930360899057</v>
+        <v>4.010116576584849</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.207488665866023</v>
+        <v>1.221032380321937</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.002806952455067</v>
+        <v>1.016378962665804</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.7845775975807</v>
+        <v>-4.771135263606148</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.265121482216195</v>
+        <v>-3.251570304368983</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.899989310628484</v>
+        <v>-6.910418946326857</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007097</t>
+          <t>X ≈ -0.007096</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.748514407512786</v>
+        <v>-5.736036766541538</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1012928986624146</v>
+        <v>0.1141657876000295</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.223726695190116</v>
+        <v>-1.211360302172388</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.959032903944397</v>
+        <v>-2.947144442088536</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.9584133230118</v>
+        <v>-10.94534259113088</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-10.66477725193644</v>
+        <v>-10.6517685341544</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.020028314971761</v>
+        <v>-7.006988995053639</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.755198991183128</v>
+        <v>-3.742038505690466</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-10.35401172403729</v>
+        <v>-10.34082998759808</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.66701348207301</v>
+        <v>-4.655197131364361</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.871690755481268</v>
+        <v>-4.859847589018123</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.699399109973051</v>
+        <v>1.712841900796647</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.326349643805351</v>
+        <v>-4.312798880569929</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.208944940789095</v>
+        <v>-2.219374576487454</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.005971</t>
+          <t>X ≈ -0.00597</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>127</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.048185609381598</v>
+        <v>1.060665450325949</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.724443356208042</v>
+        <v>5.737317813524513</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.975613877949513</v>
+        <v>2.989223564730786</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7487278748855104</v>
+        <v>0.7616763740553125</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2122083279022959</v>
+        <v>0.2252830040333862</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.294948590822877</v>
+        <v>1.307961154974798</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.996337106679569</v>
+        <v>2.009378478058998</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.67548957346753</v>
+        <v>4.688651640625487</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.402280266560858</v>
+        <v>5.415465019741688</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.126242613792563</v>
+        <v>6.141258682736016</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.494924743507696</v>
+        <v>7.510448877033014</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.80987366185613</v>
+        <v>2.823315991274278</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.39036363727044</v>
+        <v>2.403914621426992</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.215368842417924</v>
+        <v>4.204939206719594</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004845</t>
+          <t>X ≈ -0.004844</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.342228259615915</v>
+        <v>3.638756255656453</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.325904676137199</v>
+        <v>3.962698988965457</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.87699258951136</v>
+        <v>5.502854829321656</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.4159710771373</v>
+        <v>3.057760776388932</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.824148252578695</v>
+        <v>4.452666819627026</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.658982209523046</v>
+        <v>9.25804590411996</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.280199336102534</v>
+        <v>7.887523971323532</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.167012394773863</v>
+        <v>7.422841296120346</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.45927594090243</v>
+        <v>6.719391544562512</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.663721077410777</v>
+        <v>3.9376617702057</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.161550462259441</v>
+        <v>2.443488915311541</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.196598311160223</v>
+        <v>2.477985617798666</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.075241019591992</v>
+        <v>3.34844796950604</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.07895407608189231</v>
+        <v>0.3492114952644911</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.539943996580305</v>
+        <v>1.26597836723338</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.023048171673928</v>
+        <v>-4.704297350556402</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1599495292950905</v>
+        <v>0.5136224314801154</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.625976523496846</v>
+        <v>5.00823732382846</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.3302682085165</v>
+        <v>5.719041726806793</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.388501339942621</v>
+        <v>4.769585131438646</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.304925173278932</v>
+        <v>4.686156774390575</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.839215718329307</v>
+        <v>3.596491137839443</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.917862175084906</v>
+        <v>1.663444251616902</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7928005768787827</v>
+        <v>-1.059166661537439</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9974555101096172</v>
+        <v>-1.263802204614429</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.760766770566619</v>
+        <v>2.518160488803737</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4786412549254564</v>
+        <v>0.2244201797467298</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="19">
@@ -1251,202 +1251,202 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.255478093267548</v>
+        <v>-4.243019419714628</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2098778889430193</v>
+        <v>0.2227341143051689</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8297500800847502</v>
+        <v>0.8427970263427298</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.583955730644163</v>
+        <v>-2.572104342036475</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.640267295915066</v>
+        <v>-4.627209617956176</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.319709497876275</v>
+        <v>-2.306709914888295</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.418956878422293</v>
+        <v>-3.405927395577663</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.407910878968963</v>
+        <v>-5.394760340824085</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.414438380131188</v>
+        <v>-1.40126096456963</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.770474453256419</v>
+        <v>-2.758296703183873</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.510416814482824</v>
+        <v>-5.499147574713199</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.434738261167695</v>
+        <v>-2.421300799123003</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.348457620962328</v>
+        <v>-2.334909061418415</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.130288458033625</v>
+        <v>-4.140718093731891</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001468</t>
+          <t>X ≈ -0.001467</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6273305338580286</v>
+        <v>-0.4156848731159073</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.506418082873751</v>
+        <v>-4.92555263195063</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.898627172331032</v>
+        <v>-5.093020467942559</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.938040484707308</v>
+        <v>-4.135536020986564</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.64441937565725</v>
+        <v>-3.843428408370784</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.766018719009189</v>
+        <v>-3.963446737453225</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.773328549600706</v>
+        <v>-1.979436394014357</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2549892398255196</v>
+        <v>0.4528359717179029</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6387953544204947</v>
+        <v>-0.8518368168097368</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.90369587845106</v>
+        <v>-2.115964001083626</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.772774018380467</v>
+        <v>-3.978859856957484</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.075086035681927</v>
+        <v>-1.871622209403796</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.663260885600124</v>
+        <v>-1.463065715798351</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.252114249241977</v>
+        <v>0.421490975922886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.0003416</t>
+          <t>X ≈ -0.0003411</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.589234625202778</v>
+        <v>-4.788642026351184</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.762856469729876</v>
+        <v>-5.499111547355398</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.422006710736774</v>
+        <v>-3.153977813694958</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.493459893658226</v>
+        <v>-6.226369127553973</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.95412692085138</v>
+        <v>-4.94101611647644</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.197118846060363</v>
+        <v>-3.925350150693774</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.398805299810796</v>
+        <v>-5.38573904551032</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.411202632540004</v>
+        <v>-5.596854184126926</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.849367295758768</v>
+        <v>-6.576990538790135</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.32942888648396</v>
+        <v>-6.053953026789983</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.910901434237701</v>
+        <v>-7.633180347967119</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.044958077700336</v>
+        <v>-6.224241180521297</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.011894505757844</v>
+        <v>-6.188819106584475</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.662258839442956</v>
+        <v>-3.672688475141108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007842</t>
+          <t>X ≈ 0.0007849</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>258</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9952605165584245</v>
+        <v>0.8004921752560392</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2251644178455194</v>
+        <v>-0.2122546082694683</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1550783645143738</v>
+        <v>0.168085495931976</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1010981038379626</v>
+        <v>-0.08811896143949838</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.296060742326553</v>
+        <v>1.309171546701492</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.9784153422708</v>
+        <v>1.991366400841841</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4274099871062518</v>
+        <v>-0.4143437328057757</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.830640873727482</v>
+        <v>-2.815412056938534</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.732112253600313</v>
+        <v>-1.717432512483121</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9039901382910642</v>
+        <v>0.9173952659438953</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.861527774865223</v>
+        <v>1.874985068575441</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.203823101166115</v>
+        <v>-1.188960811470608</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.638051831694376</v>
+        <v>2.651180779082509</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1745948693970121</v>
+        <v>0.1641652336988599</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>291</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.988098683671467</v>
+        <v>3.00062097334709</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.117070893374624</v>
+        <v>4.129980702950675</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.378513603850557</v>
+        <v>3.391520735268159</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.508599727002945</v>
+        <v>3.521578869401409</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.654939196323838</v>
+        <v>3.668050000698777</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.553173946376354</v>
+        <v>1.566451337497028</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.526323106793264</v>
+        <v>3.53938936109374</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.059127527818255</v>
+        <v>3.071732842284128</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.968899742612749</v>
+        <v>1.982032939533525</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.833043018687775</v>
+        <v>2.846448146340606</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.343825248632058</v>
+        <v>4.357282542342276</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.974794871028458</v>
+        <v>1.988390406940155</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.098612848237337</v>
+        <v>1.911738918119056</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.379262015565168</v>
+        <v>3.368832379867015</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>301</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1547299236716384</v>
+        <v>0.1672522133472611</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7961100141976729</v>
+        <v>-0.7832002046216218</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.791693688943376</v>
+        <v>1.804700820360978</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.247869756073264</v>
+        <v>3.260848898471728</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2754162991223197</v>
+        <v>-0.2623054947473804</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3103510418080404</v>
+        <v>-0.2956872822443728</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.385559038833442</v>
+        <v>-2.372492784532966</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.005806722394986</v>
+        <v>-1.18151568917807</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.587189944890255</v>
+        <v>1.600425598383943</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4057097050163208</v>
+        <v>0.4191148326691518</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.126743216870956</v>
+        <v>-1.113285923160738</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.8988380041011936</v>
+        <v>0.9131015000953155</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.846998002192578</v>
+        <v>-1.833441955840975</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647506615</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>243</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.03689020142356725</v>
+        <v>-0.0243679117479445</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.811298608136255</v>
+        <v>0.8242084177123061</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.871430066070573</v>
+        <v>-2.858422934652971</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.973511165998637</v>
+        <v>-3.960532023600173</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.646524477869079</v>
+        <v>1.659635282244018</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.769122648155033</v>
+        <v>1.547866581882957</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.012540245697238</v>
+        <v>-1.999473991396762</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.246987820994526</v>
+        <v>-1.233806811699289</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.545045742057496</v>
+        <v>-2.528338251443458</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.749468587117327</v>
+        <v>-1.736063459464496</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7200469947861308</v>
+        <v>-0.706589701075913</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2769409494555788</v>
+        <v>-0.2613242520298371</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6971955604004805</v>
+        <v>-0.6836395140488776</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.447474228124193</v>
+        <v>-0.4579038638223452</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>228</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.409176702888992</v>
+        <v>3.421698992564615</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.419463781607952</v>
+        <v>4.432373591184003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.4585398795057</v>
+        <v>4.471547010923302</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.521232772580412</v>
+        <v>1.534211914978876</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.485436100902774</v>
+        <v>4.498546905277713</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.53796862067977</v>
+        <v>6.551011516974135</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.573030801379822</v>
+        <v>5.586097055680298</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.544270204561379</v>
+        <v>5.557451213856616</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.738140671300272</v>
+        <v>5.498148306384593</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.27056974829091</v>
+        <v>9.283974875943741</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.942794580250094</v>
+        <v>9.956251873960312</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.42264752791063</v>
+        <v>10.42825372691133</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.055024495913138</v>
+        <v>6.068580542264741</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.550359863277194</v>
+        <v>4.539930227579042</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>218</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.549907489408049</v>
+        <v>2.562429779083672</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.0247508425323133</v>
+        <v>0.03766065210836445</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.284391235868462</v>
+        <v>-1.27138410445086</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6795171407540224</v>
+        <v>0.6924962831524866</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.065488119403604</v>
+        <v>-3.052377315028664</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.227944219161174</v>
+        <v>-3.214901322866808</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.019953060416498</v>
+        <v>-1.006886806116022</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.029309435403157</v>
+        <v>-1.016128426107919</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6330345681048186</v>
+        <v>-0.6198358291500554</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.857055027252997</v>
+        <v>-2.843649899600166</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.060979946099287</v>
+        <v>-3.04752265238907</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.491725560774285</v>
+        <v>-3.472214132035646</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.994548979058663</v>
+        <v>-2.980992932707061</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9099652614613234</v>
+        <v>-0.9203948971594755</v>
       </c>
     </row>
     <row r="28">
@@ -1719,98 +1719,98 @@
         <v>156</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.548588777229632</v>
+        <v>-1.53606648755401</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.178135071717961</v>
+        <v>-3.165225262141909</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.945671608926268</v>
+        <v>-2.932664477508666</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.17867204517983</v>
+        <v>-2.165692902781366</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.082914355045041</v>
+        <v>-2.069803550670102</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4931510315500418</v>
+        <v>-0.4801081352556764</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.822957399683318</v>
+        <v>5.836023653983794</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.076290244782619</v>
+        <v>4.089471254077857</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.021281252441675</v>
+        <v>4.034479991396438</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.242944092472797</v>
+        <v>1.256349220125628</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.033055716291194</v>
+        <v>1.046513010001412</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>1.727051855246366</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.310085224658053</v>
+        <v>2.323641271009656</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.55980655693434</v>
+        <v>2.549376921236188</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.008666</t>
+          <t>X ≈ 0.008665</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>147</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5677861695859221</v>
+        <v>0.5803084592615448</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.398389427370006</v>
+        <v>4.411299236946057</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.282432285399288</v>
+        <v>1.29543941681689</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.412685418006788</v>
+        <v>1.425664560405252</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8742642029345689</v>
+        <v>0.8873750073095081</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1888380770368343</v>
+        <v>-0.1757951807424689</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.634116011996234</v>
+        <v>-1.621049757695758</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6197890245964217</v>
+        <v>0.6329700338916595</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5587891384141486</v>
+        <v>0.5719878773689118</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.110024497603916</v>
+        <v>3.123429625256747</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.585543282129876</v>
+        <v>3.599000575840094</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.259382221788272</v>
+        <v>2.272834510508382</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.83912761084337</v>
+        <v>1.852683657194973</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.408576834276076</v>
+        <v>1.398147198577924</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>109</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.034722723879646</v>
+        <v>-2.022200434204024</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.481158722165084</v>
+        <v>-5.468248912589033</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.545990919862156</v>
+        <v>0.5589980512797581</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.59367524513025</v>
+        <v>1.606654387528714</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.477272378681945</v>
+        <v>7.490383183056885</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.857283123737048</v>
+        <v>6.870326020031413</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.937687021143724</v>
+        <v>4.9507532754442</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1166523409405329</v>
+        <v>-0.1034713316452951</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7397789655376386</v>
+        <v>0.7529777044924018</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.559378551151859</v>
+        <v>3.57278367880469</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.354625226834393</v>
+        <v>3.368082520544611</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.6367148061980856</v>
+        <v>0.6501670949181957</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.638478543877035</v>
+        <v>6.652034590228638</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.888199876153379</v>
+        <v>6.877770240455227</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>99</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.998488825260509</v>
+        <v>-2.985966535584886</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.460644632482328</v>
+        <v>2.473554442058379</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.085977946087766</v>
+        <v>4.098985077505368</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.196029058493217</v>
+        <v>2.209008200891681</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.677809863623125</v>
+        <v>3.690920667998064</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.06515223906531276</v>
+        <v>-0.05210934277094736</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.159986966438609</v>
+        <v>-1.146920712138133</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.423334685284978</v>
+        <v>3.436515694580216</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.382536819304697</v>
+        <v>5.39573555825946</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.53241163427677</v>
+        <v>4.545816761929601</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.317557299858173</v>
+        <v>3.331014593568391</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.341839447102601</v>
+        <v>2.355291735822711</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.982190896763761</v>
+        <v>7.995746943115364</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.242013239141059</v>
+        <v>9.231583603442907</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>74</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2092643824927194</v>
+        <v>0.2217866721683421</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.402309230471538</v>
+        <v>-1.389399420895487</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.608227468337283</v>
+        <v>3.621234599754885</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.089831952296194</v>
+        <v>5.102811094694658</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.200059385872578</v>
+        <v>3.213170190247517</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.146149972236969</v>
+        <v>2.159192868531335</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.764118957667407</v>
+        <v>4.777185211967883</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.296935558885849</v>
+        <v>4.310116568181087</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.223523786755877</v>
+        <v>-5.210325047801113</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.073648971783804</v>
+        <v>-6.060243844130973</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.575699593398753</v>
+        <v>-3.562242299688535</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.89266778740464</v>
+        <v>-4.87921549868453</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.063201066073255</v>
+        <v>-5.073630701771407</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>57</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.155684486807566</v>
+        <v>7.168206776483188</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.035338944018747</v>
+        <v>2.048248753594798</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.658014097071316</v>
+        <v>8.671021228488918</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.788267229678759</v>
+        <v>8.801246372077223</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.495460049694337</v>
+        <v>6.508570854069276</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.979027837151378</v>
+        <v>-1.965984940857012</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3093755895114043</v>
+        <v>-0.2963093352109283</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-7.794102847942035</v>
+        <v>-7.780921838646798</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-13.11826062886118</v>
+        <v>-13.10506188990642</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-10.45961388406452</v>
+        <v>-10.44620875641169</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.401209313645275</v>
+        <v>-5.387752019935057</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.612440191387535</v>
+        <v>-3.598987902667425</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-5.787080767244746</v>
+        <v>-5.773524720893143</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.782973470056184</v>
+        <v>-3.793403105754336</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>9.531351703189401</v>
+        <v>9.544261512765452</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.68193754204734</v>
+        <v>13.69494467346494</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.81219067465485</v>
+        <v>13.82516981705331</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.728314914128141</v>
+        <v>8.741425718503081</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.57121139729833</v>
+        <v>13.58425429359269</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.5773867709351</v>
+        <v>22.59045302523558</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.56474882669912</v>
+        <v>17.57792983599436</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.95829439506226</v>
+        <v>12.97149313401702</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.10816921003432</v>
+        <v>12.12157433768715</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.44887043117134</v>
+        <v>16.46232772488156</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.02870813397122</v>
+        <v>21.04216042269133</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>20.60845352302638</v>
+        <v>20.62200956937798</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.85817485530271</v>
+        <v>20.84774521960455</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2039623664011074</v>
+        <v>0.2035654600270576</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2486795066099248</v>
+        <v>0.2482607994032904</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2596875643508696</v>
+        <v>0.2592633569889458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2561393640023297</v>
+        <v>0.2557166990231678</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2465904530222431</v>
+        <v>0.2461663766179711</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.3611584990549304</v>
+        <v>0.3607080803557849</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3390406376970887</v>
+        <v>0.3385948907357132</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3029636946118472</v>
+        <v>0.3025235134367463</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3538717906396585</v>
+        <v>0.3534185041516906</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3284154175009917</v>
+        <v>0.3279625440753762</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2604374285790172</v>
+        <v>0.2599997014672368</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.40707503385282</v>
+        <v>0.4066012915570454</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4434488277708297</v>
+        <v>0.4429631424830234</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4858165862654289</v>
+        <v>0.4859869581905727</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1095717957535101</v>
+        <v>0.1091185032594311</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2632012948613038</v>
+        <v>0.2626967907862223</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.202661942307671</v>
+        <v>0.202168939820524</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2476564434539554</v>
+        <v>0.2471531657214356</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2907657998687299</v>
+        <v>0.2902472673246308</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.4289189071797779</v>
+        <v>0.4283684407446486</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3824949318624462</v>
+        <v>0.3819550015202182</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2749452047155643</v>
+        <v>0.2744278030631193</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.326538017941246</v>
+        <v>0.3260071321296465</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.3556289708472207</v>
+        <v>0.355083720763929</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2390352502750304</v>
+        <v>0.2385169165009842</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4358423159694027</v>
+        <v>0.4352753463529382</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4503018503980911</v>
+        <v>0.4497276207476943</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4913881766347998</v>
+        <v>0.4916227476691262</v>
       </c>
     </row>
     <row r="8">
@@ -2318,101 +2318,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1172031516945538</v>
+        <v>0.1166479764256323</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3839211680443739</v>
+        <v>0.3832832568095768</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3011143851047962</v>
+        <v>0.3004928184311595</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3454757523539698</v>
+        <v>0.3448441725485765</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2437681020551992</v>
+        <v>0.2431561353865277</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3557860459506728</v>
+        <v>0.3551489042085763</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3594403747019115</v>
+        <v>0.358801181933309</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2048484531001193</v>
+        <v>0.2042427660921433</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2572933532540489</v>
+        <v>0.2566737068688312</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3180779158314095</v>
+        <v>0.3174342824260421</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1273803559424493</v>
+        <v>0.1267818852240481</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3503463561330662</v>
+        <v>0.3496923722971204</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3432075470572116</v>
+        <v>0.3425508082438355</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.4075977447105998</v>
+        <v>0.4079356526129132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01442</t>
+          <t>X &gt; -0.01441</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05361312270094487</v>
+        <v>0.05295250935526497</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3377591511631195</v>
+        <v>0.3370070357493731</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2076262645726388</v>
+        <v>0.2069015920483892</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2260530553680695</v>
+        <v>0.2253250221294394</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2288515540769893</v>
+        <v>0.228115823977717</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3391419591987628</v>
+        <v>0.3383818540503398</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3436140093916009</v>
+        <v>0.3428513806490656</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1416490506581667</v>
+        <v>0.1409310468970446</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2454226552858287</v>
+        <v>0.2446774660248963</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3146810080954339</v>
+        <v>0.313907526248677</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1744278925778318</v>
+        <v>0.1736867883532653</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.34883440930642</v>
+        <v>0.3480495021653809</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3455425100524394</v>
+        <v>0.3447528552818113</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.4082068977818452</v>
+        <v>0.4086449290066199</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3916</v>
+        <v>3917</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.01189085266098289</v>
+        <v>-0.0127226463104364</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3247233010416508</v>
+        <v>0.3237797801941369</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2492917564603943</v>
+        <v>0.2483607075327185</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2151916471922561</v>
+        <v>0.2142709120367741</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2766646535606867</v>
+        <v>0.2757192395515773</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3588121757248217</v>
+        <v>0.3578501245133907</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4155440253554872</v>
+        <v>0.4145657117336512</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2428815048317929</v>
+        <v>0.2419392907251918</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4765527243381982</v>
+        <v>0.4755495059979395</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4824734771957537</v>
+        <v>0.481454702158203</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4197349838169302</v>
+        <v>0.4187284669965479</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5962054656340143</v>
+        <v>0.5951539971190059</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5734081497119305</v>
+        <v>0.5723552930774645</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.6079194926877562</v>
+        <v>0.6084619090932222</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3851</v>
+        <v>3852</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1081666500204079</v>
+        <v>0.1070756878921415</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4522123029728391</v>
+        <v>0.4509990930728023</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3421701111354452</v>
+        <v>0.3551772425530473</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2535271159913037</v>
+        <v>0.2523625104293359</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.3251118995261635</v>
+        <v>0.3239173009946725</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.481385959714423</v>
+        <v>0.4801563190284242</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5405330077983521</v>
+        <v>0.5392857421429795</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3469394128824419</v>
+        <v>0.3457322772027069</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5337376240324687</v>
+        <v>0.5324802412836362</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5022265145974814</v>
+        <v>0.5009594753710616</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3899941750973355</v>
+        <v>0.3887514956632714</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4909925404550108</v>
+        <v>0.4897237571255175</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5527563645254858</v>
+        <v>0.5514624160382056</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6355644353409176</v>
+        <v>0.6362848212282373</v>
       </c>
     </row>
     <row r="12">
@@ -2526,361 +2526,361 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3779</v>
+        <v>3780</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1575772429659636</v>
+        <v>0.1562147711534081</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4068614177492478</v>
+        <v>0.4053919412923506</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4605415238175752</v>
+        <v>0.4735486552351773</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.262201471459008</v>
+        <v>0.2607658832562549</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.371782323171054</v>
+        <v>0.370303570658848</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4989786392984996</v>
+        <v>0.4974730705918589</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5344534760208788</v>
+        <v>0.5329356812118249</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3989027837064469</v>
+        <v>0.3974082973111663</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4847214563730518</v>
+        <v>0.4832020327800919</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5480798148933985</v>
+        <v>0.546521483564554</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4640620084993188</v>
+        <v>0.4625199724964517</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5399004592339622</v>
+        <v>0.5383384910534943</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5314934460663139</v>
+        <v>0.5299223389675589</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6375777757481984</v>
+        <v>0.6385100103693091</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.009912</t>
+          <t>X &gt; -0.009911</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1338858511723942</v>
+        <v>0.1322305211897827</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5041524873109466</v>
+        <v>0.5023468119986916</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5405506270755325</v>
+        <v>0.5535577584931346</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.308183223491838</v>
+        <v>0.306424411515458</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.539631968163647</v>
+        <v>0.5377932765314597</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7171515105975175</v>
+        <v>0.7152732207281502</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6743303023093432</v>
+        <v>0.6724600389933926</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5459781237178873</v>
+        <v>0.5441271572915056</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6620053709114799</v>
+        <v>0.6601202963284081</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7028089115854925</v>
+        <v>0.7162140392383236</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5403932750570988</v>
+        <v>0.5385107211509137</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6441494187804793</v>
+        <v>0.64223898307241</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4824433537846531</v>
+        <v>0.4805626856296499</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6935556906835103</v>
+        <v>0.6947153259639762</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.008786</t>
+          <t>X &gt; -0.008785</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2403945968036254</v>
+        <v>0.2382848573679794</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6423506431722359</v>
+        <v>0.6400655144811935</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8582537300237334</v>
+        <v>0.8712608614413355</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5165468404213485</v>
+        <v>0.5295259828198127</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7986994032851982</v>
+        <v>0.7963447029056852</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9425638540683465</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9312224323562646</v>
+        <v>0.9288368636194804</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7574316302768622</v>
+        <v>0.7550750025810302</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6841770750733858</v>
+        <v>0.6818372645946269</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7236821374738724</v>
+        <v>0.7370872651267035</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6023316488527115</v>
+        <v>0.6157889425629293</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6803412616889517</v>
+        <v>0.6779680401503896</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5540850820098271</v>
+        <v>0.5517294601657241</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.736254482964938</v>
+        <v>0.7377439552221645</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.00766</t>
+          <t>X &gt; -0.007659</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2494188226471721</v>
+        <v>0.2468760288772387</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.396274148563414</v>
+        <v>0.3936121621160993</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9445320495689842</v>
+        <v>0.9575391809865863</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7318300521393368</v>
+        <v>0.744809194537801</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.8380919295655289</v>
+        <v>0.8352707131768824</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.9513034242305238</v>
+        <v>0.9484624125178129</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.939670939855489</v>
+        <v>0.9368278400119365</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8603659420587206</v>
+        <v>0.8575220972799755</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5864361445549022</v>
+        <v>0.5836663685078562</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7094076967908549</v>
+        <v>0.722812824443686</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5905158492906821</v>
+        <v>0.6039731430008999</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.841580632214523</v>
+        <v>0.8386947412634882</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6667686328878801</v>
+        <v>0.6639115551677506</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9615575797108917</v>
+        <v>0.96333409807999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006534</t>
+          <t>X &gt; -0.006533</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4390697847119185</v>
+        <v>0.4359961674621147</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.405601274372934</v>
+        <v>0.4024454743976946</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.01309105834239</v>
+        <v>1.026098189759992</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8485328701951715</v>
+        <v>0.8615120125936357</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.211090174845019</v>
+        <v>1.207656421762096</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.318596755303183</v>
+        <v>1.315146226784854</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.191351737806592</v>
+        <v>1.187932242183876</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.006307268257558</v>
+        <v>1.002914411760869</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9323663815346137</v>
+        <v>0.9289901824231706</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8794068298104918</v>
+        <v>0.8928119574633229</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7632274647488941</v>
+        <v>0.7766847584591119</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8144569392121142</v>
+        <v>0.8110629108144352</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.824647963740766</v>
+        <v>0.8212255925751109</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.061806920636862</v>
+        <v>1.063939660318901</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005408</t>
+          <t>X &gt; -0.005407</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4153185689510792</v>
+        <v>0.4116459529367233</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1982039933188773</v>
+        <v>0.1944869762181014</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9365665271510792</v>
+        <v>0.9495736585686814</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8524245602179974</v>
+        <v>0.8654037026164616</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.250039513058624</v>
+        <v>1.24595029040897</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.31951886672136</v>
+        <v>1.31542630785296</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.15996299299637</v>
+        <v>1.155911471172168</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8632350690676063</v>
+        <v>0.8592407997087506</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7580713052686292</v>
+        <v>0.754103041741935</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6748172858848775</v>
+        <v>0.6882224135377086</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5007388081930628</v>
+        <v>0.5141961019032806</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7366497780896708</v>
+        <v>0.7326233340132049</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.7635961091081995</v>
+        <v>0.759530839148411</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9388402752373608</v>
+        <v>0.9415004514813035</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004282</t>
+          <t>X &gt; -0.004281</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3103</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2700578237488926</v>
+        <v>0.2504464373319735</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.006651277436525049</v>
+        <v>0.006258532139526096</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6913761908302689</v>
+        <v>0.7221297070808603</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7251973080086529</v>
+        <v>0.7558918281611824</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.072658673262907</v>
+        <v>1.085769477637847</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9056363804849852</v>
+        <v>0.9186792767793506</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8065900001383852</v>
+        <v>0.8196562544388613</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5503824399477963</v>
+        <v>0.5313780614091073</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4751239917373269</v>
+        <v>0.4561269805311099</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5264798112168094</v>
+        <v>0.525907524629055</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4183137373821637</v>
+        <v>0.417824723856782</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6641934216304861</v>
+        <v>0.6454395911879587</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6488705801960108</v>
+        <v>0.6302101317022561</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9815159035550991</v>
+        <v>0.971086267856947</v>
       </c>
     </row>
     <row r="19">
@@ -2890,257 +2890,257 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2005637129991129</v>
+        <v>0.1952357309832706</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2678694227579683</v>
+        <v>0.2623539929724643</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.720458343280022</v>
+        <v>0.7334654746976241</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5117284250400687</v>
+        <v>0.5247075674385329</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8396623662690885</v>
+        <v>0.8338756414614821</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7150377202291551</v>
+        <v>0.7093198011607669</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6151447374342283</v>
+        <v>0.6094489546793298</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3704021007841618</v>
+        <v>0.3647392261291671</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3961706105276264</v>
+        <v>0.3904896161499636</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5986770044470546</v>
+        <v>0.6120821320998857</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4957912522856773</v>
+        <v>0.5092485459958951</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5494591221135821</v>
+        <v>0.5436266983512184</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6581863250527675</v>
+        <v>0.6522714270854948</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.029363286178388</v>
+        <v>1.033393753876908</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.002031</t>
+          <t>X &gt; -0.00203</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5203597916273566</v>
+        <v>0.5136393233676415</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2720312923978767</v>
+        <v>0.2651963513473561</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7126148197279107</v>
+        <v>0.7256219511455129</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7338959218232333</v>
+        <v>0.7468750642216975</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.232939649857535</v>
+        <v>1.225657795906244</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9328319650257839</v>
+        <v>0.9256919257280245</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9046594982078986</v>
+        <v>0.8975149200837862</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7850934148138009</v>
+        <v>0.7779298359943496</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5261123122251661</v>
+        <v>0.5190310817004899</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8404703877503721</v>
+        <v>0.8538755154032032</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9268378785710709</v>
+        <v>0.9402951722812887</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7636255645567189</v>
+        <v>0.7563327132829016</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8739636865700575</v>
+        <v>0.8665738874770739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.399655232848616</v>
+        <v>1.40458823092677</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0009046</t>
+          <t>X &gt; -0.000904</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2505</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6303181461648748</v>
+        <v>0.6030473598357204</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.729846801405948</v>
+        <v>0.7645857744909961</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.250218842919182</v>
+        <v>1.285419485277345</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.18150659550281</v>
+        <v>1.216600042878461</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.700231532541572</v>
+        <v>1.713342336916511</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.383021252118958</v>
+        <v>1.396064148413323</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.16123320338717</v>
+        <v>1.174299457687646</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8358818387647773</v>
+        <v>0.8092063315195546</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.637720232382847</v>
+        <v>0.6509189713376102</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.103384521039132</v>
+        <v>1.139596602618099</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.377100096243076</v>
+        <v>1.413555197050364</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.035597933441856</v>
+        <v>1.009161909437594</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.117051070730078</v>
+        <v>1.09070288723332</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.509599279182183</v>
+        <v>1.499169643484031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002213</t>
+          <t>X &gt; 0.0002218</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2287</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.127853128306612</v>
+        <v>1.116990641947112</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.348740248326635</v>
+        <v>1.361650057902686</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.695581838414164</v>
+        <v>1.708588969831766</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.913095005925676</v>
+        <v>1.92607414832414</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.334534174797668</v>
+        <v>2.347644979172607</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.914927916484103</v>
+        <v>1.903308712123575</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.786545137666643</v>
+        <v>1.799611391967119</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.431362562308479</v>
+        <v>1.419840871270729</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.351399760644703</v>
+        <v>1.33989329281021</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.811890565131847</v>
+        <v>1.825295692784678</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.262445235571803</v>
+        <v>2.275902529282021</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.710526315789473</v>
+        <v>1.698659886530308</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.796592013307418</v>
+        <v>1.7845969819654</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.002587941123714</v>
+        <v>1.992158305425562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001347</t>
+          <t>X &gt; 0.001348</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2029</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.144713105552071</v>
+        <v>1.157235395227694</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.548872039293812</v>
+        <v>1.561781848869863</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.891466459540887</v>
+        <v>1.904473590958489</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.169212217517114</v>
+        <v>2.182191359915578</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.466582546201089</v>
+        <v>2.479693350576028</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.906855094476725</v>
+        <v>1.892111627998723</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.068063334902426</v>
+        <v>2.081129589202902</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.97330287107993</v>
+        <v>1.958379686193346</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.743487537714792</v>
+        <v>1.728651330151607</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.927335764799125</v>
+        <v>1.940740892451956</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.313424390259982</v>
+        <v>2.3268816839702</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.081104013953372</v>
+        <v>2.065838861436298</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.689595151235537</v>
+        <v>1.674405449360073</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.235028656996299</v>
+        <v>2.224599021298147</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1738</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.8360679943709712</v>
+        <v>0.848590284046594</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.118868663840694</v>
+        <v>1.131778473416745</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.642484457818156</v>
+        <v>1.655491589235758</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.944953434283292</v>
+        <v>1.957932576681756</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.267611438499294</v>
+        <v>2.280722242874234</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.966073284406072</v>
+        <v>1.946638178364658</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.823901313256719</v>
+        <v>1.836967567557195</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.791499087932138</v>
+        <v>1.771966700910021</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.705745908471236</v>
+        <v>1.686226676336787</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.775689728618694</v>
+        <v>1.789094856271525</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.973466594065343</v>
+        <v>1.986923887775561</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.098903761128945</v>
+        <v>2.078806352954345</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.621111750874483</v>
+        <v>1.634667797226086</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.043445281079428</v>
+        <v>2.033015645381276</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1437</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.9787839020122462</v>
+        <v>0.9913061916878689</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.519988066825768</v>
+        <v>1.532897876401819</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.611230471340292</v>
+        <v>1.624237602757894</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.672039159503342</v>
+        <v>1.685018301901806</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.800284611097837</v>
+        <v>2.813395415472776</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.442902596995111</v>
+        <v>2.41632500066342</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.705632396053616</v>
+        <v>2.718698650354092</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.377434403804422</v>
+        <v>2.39061541309966</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.730579133967318</v>
+        <v>1.704198927181473</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.062651445462336</v>
+        <v>2.076056573115167</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.622849442424311</v>
+        <v>2.636306736134529</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.350274528606576</v>
+        <v>2.32297974245369</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.347556452108435</v>
+        <v>2.361112498460038</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.597277784384723</v>
+        <v>2.58684814868657</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1194</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.185491445676313</v>
+        <v>1.198013735351935</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.664218836056541</v>
+        <v>1.677128645632592</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.523530731466629</v>
+        <v>2.536537862884231</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.821007944341687</v>
+        <v>2.833987086740152</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.03509509047354</v>
+        <v>3.048205894848479</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.580028666985179</v>
+        <v>2.593071563279544</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.665863511585819</v>
+        <v>3.678929765886295</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.115068072670539</v>
+        <v>3.128249081965777</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.600743995670861</v>
+        <v>2.565594684640324</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.838484919429554</v>
+        <v>2.851890047082385</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.303187662057582</v>
+        <v>3.316644955767799</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.88495908569962</v>
+        <v>2.848931057913916</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.967217037568794</v>
+        <v>2.980773083920397</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.216938369845082</v>
+        <v>3.206508734146929</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>966</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.6606464781354262</v>
+        <v>0.673168767811049</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.013912575615834</v>
+        <v>1.026822385191885</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.066820497767957</v>
+        <v>2.079827629185559</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.127787177428196</v>
+        <v>3.14076631982666</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.692778578695219</v>
+        <v>2.705889383070158</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.645856504001365</v>
+        <v>1.658899400295731</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.215724648156183</v>
+        <v>3.228790902456659</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.541716016696299</v>
+        <v>2.554897025991536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.860240432478832</v>
+        <v>1.873439171433596</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.320353096468487</v>
+        <v>1.333758224121318</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.736075470186066</v>
+        <v>1.749532763896283</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.10587734157528</v>
+        <v>1.060022601877257</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.238417761686271</v>
+        <v>2.251973808037874</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.902217768910795</v>
+        <v>2.891788133212643</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>748</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1100329748500997</v>
+        <v>0.1225552645257224</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.302197679642852</v>
+        <v>1.315107489218903</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.043510548480178</v>
+        <v>3.05651767989778</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.841320423410778</v>
+        <v>3.854299565809242</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.370989996055563</v>
+        <v>4.384100800430502</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.066295752195792</v>
+        <v>3.079338648490157</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.450186868034322</v>
+        <v>4.463253122334798</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.582469423858974</v>
+        <v>3.595650433154212</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.586890098424334</v>
+        <v>2.600088837379097</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.537833004184122</v>
+        <v>2.551238131836953</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.134147770654259</v>
+        <v>3.147605064364477</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.445820433436523</v>
+        <v>2.380915125932084</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.763533736930121</v>
+        <v>3.777089783281724</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.013255069206409</v>
+        <v>4.002825433508256</v>
       </c>
     </row>
     <row r="29">
@@ -3413,98 +3413,98 @@
         <v>592</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5471022203305651</v>
+        <v>0.5596245100061878</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.482825904663606</v>
+        <v>2.495735714239657</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.621740981850799</v>
+        <v>4.634748113268401</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.427669790133983</v>
+        <v>5.440648932532447</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.071681007494234</v>
+        <v>6.084791811869174</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.004258080345039</v>
+        <v>4.017300976639405</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.088443281991673</v>
+        <v>4.101509536292149</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.45234096429126</v>
+        <v>3.465521973586497</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.208908645676523</v>
+        <v>2.222107384631286</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.879053730918855</v>
+        <v>2.892458858571686</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.687813920114799</v>
+        <v>3.701271213825017</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.539764645027795</v>
+        <v>2.553216933747905</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.146537061109925</v>
+        <v>4.160093107461527</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.396258393386212</v>
+        <v>4.38582875768806</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.009229</t>
+          <t>X &gt; 0.009228</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>445</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5402695449585693</v>
+        <v>0.552791834634192</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.850044246601044</v>
+        <v>1.862954056177095</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.724838461352768</v>
+        <v>5.73784559277037</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.753967998454655</v>
+        <v>6.766947140853119</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.788580491247657</v>
+        <v>7.801691295622597</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.978816801578681</v>
+        <v>5.991883055879157</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.388037897179203</v>
+        <v>4.40121890647444</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.75400430313173</v>
+        <v>2.767203042086493</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.802755522598176</v>
+        <v>2.816160650251007</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.632385355626027</v>
+        <v>2.645837644346138</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.908759958164275</v>
+        <v>4.922316004515878</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.383200391564159</v>
+        <v>5.372770755866007</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>336</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.375609298837638</v>
+        <v>1.388131588513261</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.427991540455722</v>
+        <v>8.440970682854186</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.889570325383552</v>
+        <v>7.902681129758491</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.316564260112656</v>
+        <v>6.329630514413132</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.849380861331156</v>
+        <v>5.862561870626394</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.407428594196475</v>
+        <v>3.420627333151238</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.557303409168547</v>
+        <v>2.570708536821378</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.840645322946195</v>
+        <v>3.854102616656412</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.293242673773648</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.347631012203877</v>
+        <v>4.36118705855548</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.894971392099208</v>
+        <v>4.884541756401056</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>237</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.202764211435593</v>
+        <v>3.215286501111216</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.966718024631675</v>
+        <v>4.979627834207726</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.79125860073551</v>
+        <v>8.804265732153112</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>11.03121637469322</v>
+        <v>11.04419551709169</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.64891330308096</v>
+        <v>9.662024107455899</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.992768742906335</v>
+        <v>7.005811639200701</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.439680595254309</v>
+        <v>9.452746849554785</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.862792555122589</v>
+        <v>6.875973564417826</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.582383386239876</v>
+        <v>2.595582125194639</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.732258201211948</v>
+        <v>1.745663328864779</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.059150446514607</v>
+        <v>4.072607740224825</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.671592675590006</v>
+        <v>3.685044964310116</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.829397136375057</v>
+        <v>2.84295318272666</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.079118468651345</v>
+        <v>3.068688832953193</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>163</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.561776403716408</v>
+        <v>4.574298693392031</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.858178250874843</v>
+        <v>7.871088060450894</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.14429113937028</v>
+        <v>11.15729827078788</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.72853200203912</v>
+        <v>13.74151114443759</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.57661385445162</v>
+        <v>12.58972465882656</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.193074197075262</v>
+        <v>9.206117093369627</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.56232820986433</v>
+        <v>11.5753944641648</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.027660148506143</v>
+        <v>8.040841157801381</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.126169464777831</v>
+        <v>6.139368203732595</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.276044279749904</v>
+        <v>5.289449407402735</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.525278685493674</v>
+        <v>7.538735979203892</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.559661842839105</v>
+        <v>7.573114131559215</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.139407231894204</v>
+        <v>7.152963278245807</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.775631631655152</v>
+        <v>6.765201995957</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.166939038280589</v>
+        <v>3.179461327956211</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.98932768946728</v>
+        <v>11.00223749904333</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.48125143570087</v>
+        <v>12.49425856711847</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.38508947396875</v>
+        <v>16.39806861636722</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.84666825889659</v>
+        <v>15.85977906327152</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.20071397019714</v>
+        <v>15.21375686649151</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17.94616893217015</v>
+        <v>17.95923518647062</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.53558930697356</v>
+        <v>16.54877031626879</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.47458942079125</v>
+        <v>16.48778815974602</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.73767178293313</v>
+        <v>13.75107691058597</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.47631468503066</v>
+        <v>14.48977197874088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.56730161596099</v>
+        <v>13.5807539046811</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.09044323143119</v>
+        <v>14.10399927778279</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.45337211087728</v>
+        <v>12.44294247517913</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>11.37117854301625</v>
+        <v>11.3840883525923</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>17.05894392140811</v>
+        <v>17.07192306380657</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>17.71099889681213</v>
+        <v>17.72410970118707</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>15.6274884535754</v>
+        <v>15.64053134986976</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.39552383229171</v>
+        <v>17.40872257124647</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.16444626631139</v>
+        <v>14.17785139396422</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.95969294199381</v>
+        <v>13.97315023570403</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.61312371838687</v>
+        <v>11.62657600710698</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>12.38334529791816</v>
+        <v>12.39690134426976</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Adr Act MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Adr Act MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.445819272590931</v>
+        <v>-8.433296982915309</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.866916695078991</v>
+        <v>-8.85400688550294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-11.62973065121037</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-10.32200845954428</v>
+        <v>-10.30902931714581</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.669953484140251</v>
+        <v>-9.656842679765312</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.94394011785316</v>
+        <v>-12.93089722155879</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.457245263696869</v>
+        <v>-9.444179009396393</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.543476281525997</v>
+        <v>-7.530295272230759</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.604476167708299</v>
+        <v>-7.591277428753536</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.264125162260029</v>
+        <v>-7.250720034607198</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.087926105625229</v>
+        <v>-5.074468811915011</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.00592390066075</v>
+        <v>-10.99247161194064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.61665470208185</v>
+        <v>-12.60309865573024</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-14.74788575075793</v>
+        <v>-14.75831538645608</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.952153916540247</v>
+        <v>-2.939631626864625</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.316021107486158</v>
+        <v>-7.303111297910107</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.793458621422197</v>
+        <v>-6.780451490004594</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.580636681475248</v>
+        <v>-7.567657539076784</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.036489089207969</v>
+        <v>-9.023378284833029</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-12.40877192213451</v>
+        <v>-12.39572902584014</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.823780868764587</v>
+        <v>-8.810714614464111</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.703808304243339</v>
+        <v>-4.690627294948101</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.76480819042564</v>
+        <v>-4.751609451470877</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.532364568114112</v>
+        <v>-6.518959440461281</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.067393121789486</v>
+        <v>-3.053935828079268</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.455028313067913</v>
+        <v>-9.441576024347803</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.875282924012815</v>
+        <v>-9.861726877661212</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.46042397705763</v>
+        <v>-11.47085361275578</v>
       </c>
     </row>
     <row r="8">
@@ -4015,98 +4015,98 @@
         <v>140</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.105011933174232</v>
+        <v>-9.092102123598181</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.071309211199392</v>
+        <v>-8.058302079781789</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.655341792877607</v>
+        <v>-8.642362650479143</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.6223344365212</v>
+        <v>-5.609223632146261</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.467749641662692</v>
+        <v>-7.454706745368327</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.123911930363541</v>
+        <v>-6.110845676063065</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.930791828926694</v>
+        <v>-3.917386701273863</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.815447710184564</v>
+        <v>-4.801995421464454</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.521416606843744</v>
+        <v>-4.507860560492141</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01442</t>
+          <t>X &lt; -0.01441</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>177</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5160371902664735</v>
+        <v>-0.5035149005908508</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.082413063117734</v>
+        <v>-6.069503253541683</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.217394764064608</v>
+        <v>-4.204387632647006</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.087141631457108</v>
+        <v>-4.074162489058644</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.060591095116848</v>
+        <v>-4.047480290741909</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.458064411638475</v>
+        <v>-5.445021515344109</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.412854626085895</v>
+        <v>-4.399788371785419</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2047077378444655</v>
+        <v>0.2178887471397033</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9862356511626942</v>
+        <v>-0.973036912207931</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.96630433901548</v>
+        <v>-2.952899211362649</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3461989062709137</v>
+        <v>-0.3327416125606959</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.70164625740005</v>
+        <v>-3.68819396867994</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.55692911693253</v>
+        <v>-3.543373070580927</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.002123038893522</v>
+        <v>-5.012552674591674</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>233</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.7254457999616974</v>
+        <v>0.7379680896373202</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.319604207852343</v>
+        <v>-4.306694398276292</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.856103815736489</v>
+        <v>-3.843096684318887</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.867481584416545</v>
+        <v>-2.854502442018081</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.835087348844937</v>
+        <v>-3.821976544469997</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.396014509841713</v>
+        <v>-4.382971613547348</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.480748227113992</v>
+        <v>-4.467681972813516</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.514455231045716</v>
+        <v>-1.501274221750478</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.579746962721579</v>
+        <v>-4.566548223766816</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.000687598393284</v>
+        <v>-4.987282470740453</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.347071823998419</v>
+        <v>-4.333614530288202</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.887795962790321</v>
+        <v>-6.874343674070211</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.449681475022771</v>
+        <v>-6.436125428671168</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-7.058329241458935</v>
+        <v>-7.068758877157087</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>298</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9884215978019526</v>
+        <v>-0.9758993081263299</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.941132334512027</v>
+        <v>-4.928222524935975</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.164310169972161</v>
+        <v>-4.319649428085661</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.691775158170032</v>
+        <v>-2.678796015771567</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.565766843040862</v>
+        <v>-3.552656038665923</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.946177254318485</v>
+        <v>-4.93313435802412</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.030910971590764</v>
+        <v>-5.017844717290288</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.477960142184351</v>
+        <v>-2.464779132889113</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.216812377359936</v>
+        <v>-4.203613638405173</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.060226152991895</v>
+        <v>-4.046821025339064</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.922697598114844</v>
+        <v>-2.909240304404626</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.895025850165382</v>
+        <v>-3.881573561445272</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.650850930908945</v>
+        <v>-4.637294884557342</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.743411477827287</v>
+        <v>-5.753841113525439</v>
       </c>
     </row>
     <row r="12">
@@ -4223,358 +4223,358 @@
         <v>370</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.280500314819136</v>
+        <v>-1.267978025143513</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.431157485734886</v>
+        <v>-3.418247676158835</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.621644397841095</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.207465345001161</v>
+        <v>-2.194486202602697</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.286427100613878</v>
+        <v>-3.273316296238939</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.070066243979298</v>
+        <v>-4.057023347684932</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.884529690981296</v>
+        <v>-3.87146343668082</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.459821197870916</v>
+        <v>-2.446640188575678</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.791091354323484</v>
+        <v>-2.777892615368721</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.641216539351412</v>
+        <v>-3.62781141169858</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.035159052858177</v>
+        <v>-3.021701759147959</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.541316436053293</v>
+        <v>-3.527864147333183</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.421030506457647</v>
+        <v>-3.407474460106044</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.522660525532707</v>
+        <v>-4.533090161230859</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.009912</t>
+          <t>X &lt; -0.009911</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>449</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8304671450436842</v>
+        <v>-0.8179448553680615</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.550688208118807</v>
+        <v>-3.537778398542756</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.277658417548601</v>
+        <v>-4.376008763342135</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.147405284941094</v>
+        <v>-2.13442614254263</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.019159833346606</v>
+        <v>-4.006049028971667</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.055051228964274</v>
+        <v>-5.042008332669909</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.25089605734766</v>
+        <v>-4.237829803047184</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.162523900573611</v>
+        <v>-3.149342891278373</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.667968231200355</v>
+        <v>-3.654769492245592</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.180553203409673</v>
+        <v>-4.28246606635323</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.049003632404315</v>
+        <v>-3.035546338694097</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.682771922720356</v>
+        <v>-3.669319634000246</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.321289339901334</v>
+        <v>-2.307733293549731</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.076022350609456</v>
+        <v>-4.086451986307608</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.008786</t>
+          <t>X &lt; -0.008785</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>555</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.330647622535551</v>
+        <v>-1.318125332859928</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.657784741760999</v>
+        <v>-3.644874932184948</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.395937987441073</v>
+        <v>-5.470773329462347</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.023128404829393</v>
+        <v>-3.102168078026509</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.818282115413233</v>
+        <v>-4.805171311038293</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.418506245920192</v>
+        <v>-5.405463349625826</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.964640322258894</v>
+        <v>-4.951574067958418</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.816024798239681</v>
+        <v>-3.802843788944443</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.979358616199356</v>
+        <v>-2.966159877244593</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.375807245165127</v>
+        <v>-3.457012246285409</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.76488878258791</v>
+        <v>-2.847678815340842</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.090865985602832</v>
+        <v>-3.077413696882722</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.249859335286473</v>
+        <v>-2.23630328893487</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.441579444451627</v>
+        <v>-3.452009080149779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.00766</t>
+          <t>X &lt; -0.007659</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>658</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.133921703895773</v>
+        <v>-1.12139941422015</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.688093504171206</v>
+        <v>-1.675183694595155</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.878095465792001</v>
+        <v>-4.940045713791285</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.612051749587565</v>
+        <v>-3.67586167792674</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.150472964659734</v>
+        <v>-4.137362160284795</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.459091633004682</v>
+        <v>-4.446048736710317</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.089279895731501</v>
+        <v>-4.076213641431025</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.647372385422095</v>
+        <v>-3.634191376126857</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.890190453422576</v>
+        <v>-1.876991714467813</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.659384935365026</v>
+        <v>-2.726910510797673</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.175058831055821</v>
+        <v>-2.243700692831268</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.356481144835016</v>
+        <v>-3.343028856114906</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.408954600764723</v>
+        <v>-2.39539855441312</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.982941475175359</v>
+        <v>-3.993371110873511</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006534</t>
+          <t>X &lt; -0.006533</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>765</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.778223755840656</v>
+        <v>-1.765701466165034</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.439212193252253</v>
+        <v>-1.426302383676202</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.369672306437486</v>
+        <v>-4.421854002501462</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.522169880044679</v>
+        <v>-3.575398364764858</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.103615866955181</v>
+        <v>-5.090505062580242</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.327686315158687</v>
+        <v>-5.314643418864321</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.499773357072421</v>
+        <v>-4.486707102771945</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.663175791056005</v>
+        <v>-3.649994781760768</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.072285194839353</v>
+        <v>-3.059086455884589</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.940489702854329</v>
+        <v>-2.996358576855904</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.552912100022986</v>
+        <v>-2.609592521973454</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.649247896925921</v>
+        <v>-2.635795608205811</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.677345645125726</v>
+        <v>-2.663789598774123</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.734813855333094</v>
+        <v>-3.745243491031246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005408</t>
+          <t>X &lt; -0.005407</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>892</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.377366891638545</v>
+        <v>-1.364844601962922</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.4219762188885241</v>
+        <v>-0.409066409312473</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.326696282228923</v>
+        <v>-3.370802079781789</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.91548880470247</v>
+        <v>-2.960000320072119</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.3487646059044</v>
+        <v>-4.33565380152946</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.386893137987386</v>
+        <v>-4.37385024169302</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.576772269129926</v>
+        <v>-3.563706014829449</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.477960142184351</v>
+        <v>-2.464779132889113</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.867819088769338</v>
+        <v>-1.854620349814574</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.650356698547562</v>
+        <v>-1.697827736748458</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.121451623455677</v>
+        <v>-1.16976023195447</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.871821829338948</v>
+        <v>-1.858369540618838</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.955753570328689</v>
+        <v>-1.942197523977086</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.602893224599491</v>
+        <v>-2.613322860297643</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004282</t>
+          <t>X &lt; -0.004281</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6839145106861722</v>
+        <v>-0.6255401979939137</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2759404477781544</v>
+        <v>0.2371081523295047</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.97366519649151</v>
+        <v>-2.060612804261879</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.984131323957222</v>
+        <v>-2.070934079050566</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.999651775670607</v>
+        <v>-3.03602466714559</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.320530448641968</v>
+        <v>-2.357335098902304</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.832745081944786</v>
+        <v>-1.870072150256171</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.059470465459107</v>
+        <v>-1.002536408914224</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6433711150001926</v>
+        <v>-0.5868741421767467</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8683003566931049</v>
+        <v>-0.8648196305943046</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6378669232524672</v>
+        <v>-0.6351740100247909</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.272699827092509</v>
+        <v>-1.216240202471404</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.214942965762077</v>
+        <v>-1.158836136969157</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.208051461401659</v>
+        <v>-2.174743275663353</v>
       </c>
     </row>
     <row r="19">
@@ -4587,254 +4587,254 @@
         <v>1207</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3877405497723245</v>
+        <v>-0.3752182600967018</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4303628828026405</v>
+        <v>-0.4174530732265893</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.689963284398914</v>
+        <v>-1.720564672680226</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.102464562581019</v>
+        <v>-1.133507868897084</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.889024735469569</v>
+        <v>-1.87591393109463</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.426156825876319</v>
+        <v>-1.413113929581954</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.014612627515852</v>
+        <v>-1.001546373215376</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4065272090930563</v>
+        <v>-0.3933461997978185</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3021011233977688</v>
+        <v>-0.2889023844430056</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8584171837043755</v>
+        <v>-0.8906822229564852</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.68602449991252</v>
+        <v>-0.7185873864971626</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7344913839921077</v>
+        <v>-0.7210390952719976</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9890459120869721</v>
+        <v>-0.9754898657353692</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.899225159760974</v>
+        <v>-1.909654795459126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.002031</t>
+          <t>X &lt; -0.00203</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1404</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9309383202099752</v>
+        <v>-0.9184160305343525</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3408073877196927</v>
+        <v>-0.3278975781436415</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.337122999401238</v>
+        <v>-1.36187350835322</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.311306027789207</v>
+        <v>-1.33603713519841</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.276469774867074</v>
+        <v>-2.263358970492135</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.552285305145716</v>
+        <v>-1.539242408851351</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.35252400108088</v>
+        <v>-1.339457746780404</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.108469846519554</v>
+        <v>-1.095288837224317</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4582321793590438</v>
+        <v>-0.4450334404042806</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.127029754701994</v>
+        <v>-1.152704726065579</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.363872381571497</v>
+        <v>-1.389500162533544</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9733638681007193</v>
+        <v>-0.9599115793806092</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.179943265370412</v>
+        <v>-1.166387219018809</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.212273215145402</v>
+        <v>-2.222702850843554</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0009046</t>
+          <t>X &lt; -0.000904</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8864037538060856</v>
+        <v>-0.8445523941707194</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9496721273489896</v>
+        <v>-1.001193032689095</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.858714883850972</v>
+        <v>-1.909553920724349</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.69648048407705</v>
+        <v>-1.747425063793983</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.477915064884343</v>
+        <v>-2.496637978577006</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.876706419999785</v>
+        <v>-1.895681678146531</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.414660064368057</v>
+        <v>-1.433943949981007</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9097900002090853</v>
+        <v>-0.8688328730634396</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4847631549211613</v>
+        <v>-0.5047998504726721</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.240822224063479</v>
+        <v>-1.294002192643454</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.716358500480979</v>
+        <v>-1.769197736291567</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.134530087661091</v>
+        <v>-1.093788734534364</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.250648445564643</v>
+        <v>-1.209988220066606</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.852508621804162</v>
+        <v>-1.83531639962731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002213</t>
+          <t>X &lt; 0.0002218</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.316967731974685</v>
+        <v>-1.304445442299063</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.510041360675565</v>
+        <v>-1.525257203812089</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.037353873175533</v>
+        <v>-2.052416579514272</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.253933881025127</v>
+        <v>-2.268853932216672</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.764425999834629</v>
+        <v>-2.779244291722357</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.145440653758847</v>
+        <v>-2.132397757464481</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.880327096966369</v>
+        <v>-1.895564708370522</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.43598234561383</v>
+        <v>-1.422801336318592</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.228885717050822</v>
+        <v>-1.215686978096059</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.835451546891129</v>
+        <v>-1.851128562629668</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.440506429220051</v>
+        <v>-2.455932126854727</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.708324023350727</v>
+        <v>-1.694871734630617</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.806517442669218</v>
+        <v>-1.792961396317615</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.064391300346195</v>
+        <v>-2.050317533530702</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001347</t>
+          <t>X &lt; 0.001348</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.036671402916745</v>
+        <v>-1.048318566936423</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.354659323865349</v>
+        <v>-1.366538213823752</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.771752699977789</v>
+        <v>-1.783535473562438</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.99315691892803</v>
+        <v>-2.004813933908785</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.271513882310813</v>
+        <v>-2.283173211978195</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.644505089604571</v>
+        <v>-1.631462193310206</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.704290101415282</v>
+        <v>-1.716172552576374</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.60623562925943</v>
+        <v>-1.593054619964192</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.290410268150168</v>
+        <v>-1.277211529195405</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.502489688089213</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.91725189534705</v>
+        <v>-1.929412485897323</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.647130878501393</v>
+        <v>-1.633678589781283</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.265876767145492</v>
+        <v>-1.25232072079389</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.791910907990633</v>
+        <v>-1.780946220968104</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5512895598794003</v>
+        <v>-0.5602221024054828</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6945117264772449</v>
+        <v>-0.7036723715320647</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.150004709249728</v>
+        <v>-1.159052094545856</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.328667639558859</v>
+        <v>-1.337624377998935</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.555399715612971</v>
+        <v>-1.564362824769951</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.25795777789731</v>
+        <v>-1.244914881602945</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.072152095995001</v>
+        <v>-1.081280870008193</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.042441084838615</v>
+        <v>-1.029260075543377</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.8964016335468088</v>
+        <v>-0.8832028945920456</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9783714241450596</v>
+        <v>-0.9877800760150635</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.160292059880945</v>
+        <v>-1.169667454752421</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.208793278830584</v>
+        <v>-1.195340990110473</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8599619752398624</v>
+        <v>-0.8695324567682619</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.167766851269484</v>
+        <v>-1.159642086290248</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4728652122011567</v>
+        <v>-0.4794470624844038</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.705526449896027</v>
+        <v>-0.712234379292525</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8234100515355323</v>
+        <v>-0.8301296641782798</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8205285737319201</v>
+        <v>-0.8272366000589741</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.412831650859481</v>
+        <v>-1.419395439008028</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.152181471789881</v>
+        <v>-1.139138575495515</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.217239655270205</v>
+        <v>-1.223848934761683</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.038812560367425</v>
+        <v>-1.045551945382158</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6211673802758</v>
+        <v>-0.6079686413210368</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8250301872534465</v>
+        <v>-0.8319669663695919</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.156810549601786</v>
+        <v>-1.163655867952897</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9750434571052864</v>
+        <v>-0.9615911683851763</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9694709483739388</v>
+        <v>-0.9764362000331488</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.104817904150266</v>
+        <v>-1.098774902367133</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4367963782005333</v>
+        <v>-0.4418192998299375</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5805599938824955</v>
+        <v>-0.5856961896804478</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9911087099462605</v>
+        <v>-0.9961483818776742</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.079043639461666</v>
+        <v>-1.084043776370798</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.160580795159191</v>
+        <v>-1.165609534465347</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9125318098491135</v>
+        <v>-0.9176179057811638</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.283178339629949</v>
+        <v>-1.288150640602069</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.056406969177871</v>
+        <v>-1.061505053440534</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.7794548445457039</v>
+        <v>-0.7662561055909407</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.9012351786803947</v>
+        <v>-0.9064756792104305</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.121148322479506</v>
+        <v>-1.126337835386465</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9176748709169686</v>
+        <v>-0.9042225821968586</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9470883640446033</v>
+        <v>-0.9523747882326177</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.050762231299387</v>
+        <v>-1.046091660700554</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.161669932103564</v>
+        <v>-0.1655217877308459</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2227326595361632</v>
+        <v>-0.2266874131130407</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6007262395202702</v>
+        <v>-0.6045942347151509</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8921838981407646</v>
+        <v>-0.8959530938597595</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7557453690546723</v>
+        <v>-0.7595995719958921</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3786318628897334</v>
+        <v>-0.3825842580154983</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.7912953465710402</v>
+        <v>-0.795126912068433</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5828501239111219</v>
+        <v>-0.5867840954175989</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3129495790370598</v>
+        <v>-0.3169749850658903</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.172832901476248</v>
+        <v>-0.1769680361611279</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.32863777490833</v>
+        <v>-0.3327416125606959</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1058715720369889</v>
+        <v>-0.09241928331687888</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.445680784876771</v>
+        <v>-0.4497757881216558</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.649550846579487</v>
+        <v>-0.6460875807609483</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0116891336429461</v>
+        <v>0.008832065540630651</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2070048991765816</v>
+        <v>-0.2098870635337136</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6447062041214551</v>
+        <v>-0.6474831214833543</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7919148971926475</v>
+        <v>-0.7946430877200044</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9039419460548004</v>
+        <v>-0.9066681231391414</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5613110098719432</v>
+        <v>-0.5641229964683561</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8062885499283041</v>
+        <v>-0.8090348108719212</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6117311818419537</v>
+        <v>-0.6145615587277433</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3336559453462229</v>
+        <v>-0.3365728458046746</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3450943301857237</v>
+        <v>-0.3480558852470139</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.504085516789047</v>
+        <v>-0.5070131575028398</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3227731793084487</v>
+        <v>-0.3093208905883387</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6090121388837275</v>
+        <v>-0.611928399793598</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.6662430966365989</v>
+        <v>-0.6636651806947711</v>
       </c>
     </row>
     <row r="29">
@@ -5104,101 +5104,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3557</v>
+        <v>3558</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.05646353029400331</v>
+        <v>-0.05862535565336202</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3364493105908721</v>
+        <v>-0.3386007230379562</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7442752586049082</v>
+        <v>-0.7463299387258786</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8512647373287265</v>
+        <v>-0.8532851360653027</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.954038626890565</v>
+        <v>-0.9560537014321824</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5573108518410095</v>
+        <v>-0.5594259185115007</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5146446544295955</v>
+        <v>-0.5167763512784447</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4052968447218035</v>
+        <v>-0.4074798160819668</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.142108851326384</v>
+        <v>-0.1443693924545286</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2747160877624921</v>
+        <v>-0.2769760170675681</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4357056668879338</v>
+        <v>-0.4379301189314972</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2170452696916456</v>
+        <v>-0.2193308949796986</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4810247333995932</v>
+        <v>-0.483254932908153</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5247576465502704</v>
+        <v>-0.5227898102897086</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.009229</t>
+          <t>X &lt; 0.009228</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.03177568905581296</v>
+        <v>-0.03336358298190589</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1491454100310605</v>
+        <v>-0.1507515720781427</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.66407983223381</v>
+        <v>-0.6655602683101662</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7616576633291885</v>
+        <v>-0.7631086608617679</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8816549705522121</v>
+        <v>-0.8830908527016916</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5427188534853471</v>
+        <v>-0.5442377368653837</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.558989114026005</v>
+        <v>-0.5605070061123172</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3646802348054123</v>
+        <v>-0.3662655536335393</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1143299339654078</v>
+        <v>-0.1159854251596428</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1405313881808183</v>
+        <v>-0.1422066373367272</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2762442167920014</v>
+        <v>-0.2778899862099706</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1188167642281925</v>
+        <v>-0.1205048052557345</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3889701059761919</v>
+        <v>-0.3905989769596445</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.448029739238855</v>
+        <v>-0.4465744957678268</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.08883821566215033</v>
+        <v>-0.09000931509144294</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3010903645467735</v>
+        <v>-0.3022432631695438</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6295877527415286</v>
+        <v>-0.6306643580264222</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.694503259190526</v>
+        <v>-0.6955604986560644</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6432658860240821</v>
+        <v>-0.6443493748315205</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3316222255038639</v>
+        <v>-0.3327810520140559</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4021467845146205</v>
+        <v>-0.4032896884756667</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3576011459257984</v>
+        <v>-0.358766975048006</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.08994599733737374</v>
+        <v>-0.0911839113780033</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.03487506557478071</v>
+        <v>-0.03614745858884305</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1725322751370513</v>
+        <v>-0.1737739256293409</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.09723014793029705</v>
+        <v>-0.09849137833776211</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1881332148293708</v>
+        <v>-0.1893808750399799</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2383132356779427</v>
+        <v>-0.237252635188824</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1622281291271719</v>
+        <v>-0.1630352358323677</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2314135641630202</v>
+        <v>-0.2322295121332161</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5105867320471447</v>
+        <v>-0.5113383401575007</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6215397968114544</v>
+        <v>-0.6222614160011588</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5341645090245848</v>
+        <v>-0.5349175201043082</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3256944671594084</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4212909993680185</v>
+        <v>-0.4220701658589761</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2620644825031633</v>
+        <v>-0.2628922661188966</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.04836796713737357</v>
+        <v>0.04745953617026544</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.08059004762372268</v>
+        <v>0.07965914284881848</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08427713645901491</v>
+        <v>-0.0851697214923206</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.03553676778000181</v>
+        <v>-0.03644169039347389</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.01857828198835421</v>
+        <v>0.01765225066196052</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.001603001798301307</v>
+        <v>0.002311583473208145</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3986</v>
+        <v>3987</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1553537990796983</v>
+        <v>-0.1559160305343497</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2530859701927355</v>
+        <v>-0.2536425086944618</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4343314778994127</v>
+        <v>-0.4348474953467161</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5157736533094734</v>
+        <v>-0.5162680795509544</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4649949049639019</v>
+        <v>-0.4655084884311194</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2791095386510349</v>
+        <v>-0.2796665165108223</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3251927432145933</v>
+        <v>-0.3257394452883275</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1775539606938494</v>
+        <v>-0.1781432919796018</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.04938196766295277</v>
+        <v>-0.05000440651858185</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.03354872115727403</v>
+        <v>-0.0341852122091808</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1490465678487212</v>
+        <v>-0.1496567818398304</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1256640735603938</v>
+        <v>-0.1262800613670336</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1054575972052803</v>
+        <v>-0.106083801644175</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.09242497136339267</v>
+        <v>-0.09189953493865488</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05260991784310676</v>
+        <v>-0.05301363960509065</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2209182217069028</v>
+        <v>-0.2212934450972028</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3064913945808811</v>
+        <v>-0.3068488474407687</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3849248177974189</v>
+        <v>-0.3852620796143924</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3670812987409207</v>
+        <v>-0.3674274318008486</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3030284088101354</v>
+        <v>-0.3033881725295089</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3249701314217432</v>
+        <v>-0.3253253459858385</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2847763085755801</v>
+        <v>-0.2851453604141696</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2334052096808179</v>
+        <v>-0.2337876311550602</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1803947093672349</v>
+        <v>-0.180797203814798</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2230389743021064</v>
+        <v>-0.2234327711087687</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1747978779401578</v>
+        <v>-0.1752035282365654</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1855398228957412</v>
+        <v>-0.1859463807287653</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1444559544020905</v>
+        <v>-0.1440720630139438</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.06577770226000013</v>
+        <v>-0.0661084796640381</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1682937580454578</v>
+        <v>-0.1686102158002427</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2309895700946711</v>
+        <v>-0.2312934249585723</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3082778139117863</v>
+        <v>-0.3085620055891951</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3179652661726564</v>
+        <v>-0.3182508012961378</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2280877567761479</v>
+        <v>-0.2283935396736751</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2012344114188238</v>
+        <v>-0.2015475104427793</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1883160892250473</v>
+        <v>-0.1886356221231651</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1620987253308499</v>
+        <v>-0.1624252688770582</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1139537149639835</v>
+        <v>-0.1142978981850646</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1328762390709386</v>
+        <v>-0.1332173051683014</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06009978788311088</v>
+        <v>-0.06045868877727401</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.07302928339493064</v>
+        <v>-0.07338797627772919</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.03078857978622551</v>
+        <v>-0.03049115297518767</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/adr_act_ma_ratio_30.xlsx
@@ -568,989 +568,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01723</t>
+          <t>X ≈ -0.01722</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.46997155194513</v>
+        <v>15.44100285496527</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.085172847734668</v>
+        <v>-2.086376760488427</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.488004948092154</v>
+        <v>9.487918109163914</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.639926221914493</v>
+        <v>1.639440562294368</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-6.879068797206237</v>
+        <v>-6.830677893691039</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-10.57591257289909</v>
+        <v>-10.55206425161619</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.670133416472865</v>
+        <v>-6.622241302353601</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.843914138229358</v>
+        <v>4.893103942951036</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.784192677796533</v>
+        <v>4.857370694128022</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.0559044558631</v>
+        <v>-3.956670459456411</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.732477063412929</v>
+        <v>3.832315612142821</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.228272925651375</v>
+        <v>-4.104645784866968</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6504471242208041</v>
+        <v>-0.5017963084681014</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.25298329355428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01611</t>
+          <t>X ≈ -0.01609</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.8648552837231449</v>
+        <v>0.6132601167408112</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.33574607223404</v>
+        <v>-13.42742487742148</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-12.51650051916805</v>
+        <v>-10.70717693786661</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12.38965126578853</v>
+        <v>-10.58021073921256</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.381713043834239</v>
+        <v>4.519134889615238</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.899669779765645</v>
+        <v>7.911497790833707</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.377013599698202</v>
+        <v>1.613588151873657</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.3532019402763</v>
+        <v>10.50962464799193</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.294621173930665</v>
+        <v>10.47530435922523</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.225220744471351</v>
+        <v>3.411058388797571</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.69198386554994</v>
+        <v>12.5757531207141</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.50584715163729</v>
+        <v>9.513610503872904</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.31356691560296</v>
+        <v>12.24503612507879</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.31695343074674</v>
+        <v>9.372016706442487</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01497</t>
+          <t>X ≈ -0.01496</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.956163940494889</v>
+        <v>5.804625964135646</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.352348831733472</v>
+        <v>4.228425661670641</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.35016693785663</v>
+        <v>9.37676877694102</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13.17861672971713</v>
+        <v>12.27953672799282</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.858160384770095</v>
+        <v>3.479654756473238</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.155567560388967</v>
+        <v>3.752927422689474</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.071464979292649</v>
+        <v>3.693230810100189</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.002552505609572</v>
+        <v>6.002263150523937</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.544810595327746</v>
+        <v>0.4182661665841607</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6961316416876926</v>
+        <v>2.370384600864604</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.909790550785409</v>
+        <v>-3.384607954636294</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5261011029306033</v>
+        <v>2.225525378391744</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1060985681929481</v>
+        <v>1.830933332375196</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.331774703635233</v>
+        <v>2.080350039775979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01385</t>
+          <t>X ≈ -0.01384</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.646695094043828</v>
+        <v>4.617642643591203</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.262206321639795</v>
+        <v>1.261028423969456</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.693015467810447</v>
+        <v>-2.69319274042941</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9985205441457978</v>
+        <v>0.9980313101876277</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.10157308321488</v>
+        <v>-3.053166677181075</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.023354135302569</v>
+        <v>-0.9994576007993174</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.673309956106706</v>
+        <v>-4.625414833906859</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.924234865153792</v>
+        <v>-6.875097144557905</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-15.90399718708998</v>
+        <v>-15.83089652892101</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-11.40541904585182</v>
+        <v>-11.30621236755941</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.96610348389203</v>
+        <v>-16.86631273288488</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-16.93602740378761</v>
+        <v>-16.81242217627084</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-15.57522480267463</v>
+        <v>-15.42658667641416</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-13.56783919597908</v>
+        <v>-13.39584043641242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01273</t>
+          <t>X ≈ -0.01272</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.11215623628464</v>
+        <v>-7.031932134869443</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.215432423015663</v>
+        <v>-7.100525714165066</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.081751490903258</v>
+        <v>-5.984427725850303</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.043095811165053</v>
+        <v>-2.834099563501994</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.580572032430481</v>
+        <v>-3.322863673723397</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.890203125823561</v>
+        <v>-7.587456455688958</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.976535167292468</v>
+        <v>-7.649956286325136</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.908992769450123</v>
+        <v>-6.60461618766508</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.898253452778782</v>
+        <v>-3.616626461908922</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6744281657791475</v>
+        <v>-1.413487570907947</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.19520990662334</v>
+        <v>1.409944550368884</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.843112219502558</v>
+        <v>6.011531798952163</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.81049932931154</v>
+        <v>1.073596649875817</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.040366668508767</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.0116</t>
+          <t>X ≈ -0.01159</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>72</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.472726183323992</v>
+        <v>-2.50115794297777</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.84537456154667</v>
+        <v>2.843576355404053</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.859321923258513</v>
+        <v>-5.857886039864439</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1888145629840636</v>
+        <v>-0.1892754872718143</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.11136185637455</v>
+        <v>-2.062924338365214</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4289731380523136</v>
+        <v>-0.4050484322691759</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8726639410278878</v>
+        <v>0.9206047159192607</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.367258778491795</v>
+        <v>-2.318085879240947</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.11958618771979</v>
+        <v>3.192764606740177</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.891045954787231</v>
+        <v>-1.791805007138947</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.484093538078383</v>
+        <v>-3.384268613481808</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.062549774093057</v>
+        <v>-1.938920486277873</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.682316462246987</v>
+        <v>1.830967739011349</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5194623913223211</v>
+        <v>0.691461150888351</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01048</t>
+          <t>X ≈ -0.01047</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.279831342233869</v>
+        <v>1.82613347227997</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.136759659773048</v>
+        <v>-4.75919962253348</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.274725916381307</v>
+        <v>-2.665559606218999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.878249472279272</v>
+        <v>-1.286251559255646</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.476271131043916</v>
+        <v>-6.771287546185498</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-9.70605041870418</v>
+        <v>-8.994198048433603</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.00351556118779</v>
+        <v>-5.314482215307422</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.476091712653336</v>
+        <v>-6.339187155190636</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.805082693705288</v>
+        <v>-7.626131432702884</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.403252548696415</v>
+        <v>-7.202538651967089</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.097502315733408</v>
+        <v>-3.66169952868276</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.329202280617828</v>
+        <v>-4.853963133306685</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.842328376988064</v>
+        <v>2.247508305608562</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.994602306287312</v>
+        <v>-2.502983293555531</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.009348</t>
+          <t>X ≈ -0.00934</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.464612295419926</v>
+        <v>-2.987954299943503</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.168395975025732</v>
+        <v>-4.079256599802683</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-10.22137294998601</v>
+        <v>-10.01328445480974</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.260086426589652</v>
+        <v>-7.116369792133682</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.231002740594214</v>
+        <v>-8.529967303234017</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.993310051517334</v>
+        <v>-7.33574277903702</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-8.022584154693327</v>
+        <v>-8.322991045390111</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.610188916443093</v>
+        <v>-6.939469758770663</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.07641273119077852</v>
+        <v>-0.5058148291741205</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.008296614061528373</v>
+        <v>-0.4040965027480397</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.082387448435831</v>
+        <v>-2.458823473473757</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5695153583930121</v>
+        <v>-1.476057345316654</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.933065186608061</v>
+        <v>-2.797411595739675</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.7646046946317568</v>
+        <v>-1.623353663926885</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008222</t>
+          <t>X ≈ -0.008214</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.05298087962543008</v>
+        <v>-0.5845170668952733</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.995551984956101</v>
+        <v>8.382406224299032</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.053825467218672</v>
+        <v>-2.554200194243997</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.769201932900678</v>
+        <v>-7.221811813817794</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5233604220169923</v>
+        <v>-0.9961199187799465</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7425855423641465</v>
+        <v>0.2355240832495937</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6579194892268561</v>
+        <v>0.1747366931789571</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.718179897309376</v>
+        <v>-3.170249990460881</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.010116576584849</v>
+        <v>3.512755989924223</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.221032380321937</v>
+        <v>0.7698501738742394</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.016378962665804</v>
+        <v>0.5658001452016777</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.771135263606148</v>
+        <v>-5.141980789922549</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.251570304368983</v>
+        <v>-3.616210513908733</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.910418946326857</v>
+        <v>-7.214521755094772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007096</t>
+          <t>X ≈ -0.00709</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.736036766541538</v>
+        <v>-5.761671287282013</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1141657876000295</v>
+        <v>1.044882857197301</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.211360302172388</v>
+        <v>-0.2777761098821685</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.947144442088536</v>
+        <v>-2.013330442703456</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.94534259113088</v>
+        <v>-9.961054480970269</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-10.6517685341544</v>
+        <v>-9.691772848884362</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.006988995053639</v>
+        <v>-6.956704591588391</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.742038505690466</v>
+        <v>-3.690116753121963</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-10.34082998759808</v>
+        <v>-10.26121775245867</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.655197131364361</v>
+        <v>-4.552772771431357</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.859847589018123</v>
+        <v>-4.758385423723219</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.712841900796647</v>
+        <v>1.836498608979277</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.312798880569929</v>
+        <v>-4.164140907991865</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.219374576487454</v>
+        <v>-2.047375816920585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00597</t>
+          <t>X ≈ -0.005964</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>127</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.060665450325949</v>
+        <v>1.815923897888275</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.737317813524513</v>
+        <v>5.731277548412152</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.989223564730786</v>
+        <v>2.987189608728208</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7616763740553125</v>
+        <v>-0.02402766861789729</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2252830040333862</v>
+        <v>0.2739866626134102</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.307961154974798</v>
+        <v>0.5461466596178468</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.009378478058998</v>
+        <v>2.057092061071785</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.688651640625487</v>
+        <v>4.735626647777345</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.415465019741688</v>
+        <v>5.485917691812695</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.141258682736016</v>
+        <v>6.237307740066946</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.510448877033014</v>
+        <v>7.608249438835351</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.823315991274278</v>
+        <v>2.946971160298851</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.403914621426992</v>
+        <v>2.552573925540457</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.204939206719594</v>
+        <v>4.376937966286611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004844</t>
+          <t>X ≈ -0.004839</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.638756255656453</v>
+        <v>3.323616189640454</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.962698988965457</v>
+        <v>3.686575580012111</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.502854829321656</v>
+        <v>5.23934172385718</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.057760776388932</v>
+        <v>3.427699978344421</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.452666819627026</v>
+        <v>4.236796754134609</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>9.25804590411996</v>
+        <v>9.693310679372956</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.887523971323532</v>
+        <v>8.338931518447254</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.422841296120346</v>
+        <v>7.873452069177937</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.719391544562512</v>
+        <v>7.19029195826139</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.9376617702057</v>
+        <v>4.423936910265901</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.443488915311541</v>
+        <v>2.923586027282134</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.477985617798666</v>
+        <v>2.982623856735842</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.34844796950604</v>
+        <v>3.886590635495068</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3492114952644911</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003719</t>
+          <t>X ≈ -0.003714</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.26597836723338</v>
+        <v>1.196301918015067</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.704297350556402</v>
+        <v>-4.723880125959909</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5136224314801154</v>
+        <v>-0.1687836282666169</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.00823732382846</v>
+        <v>4.916579560489488</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.719041726806793</v>
+        <v>5.664894751205104</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.769585131438646</v>
+        <v>4.701313100705001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.686156774390575</v>
+        <v>4.642143257693178</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.596491137839443</v>
+        <v>3.55537575681614</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.663444251616902</v>
+        <v>1.383114298427735</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.059166661537439</v>
+        <v>-1.300034692094599</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.263802204614429</v>
+        <v>-1.504677316205104</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.518160488803737</v>
+        <v>2.277135248072639</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2244201797467298</v>
+        <v>0.01992463656321775</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.3523621755435329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002593</t>
+          <t>X ≈ -0.002589</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.243019419714628</v>
+        <v>-4.776378020174398</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2227341143051689</v>
+        <v>0.7274318630376726</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8427970263427298</v>
+        <v>1.348588770855415</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.572104342036475</v>
+        <v>-2.571478444988706</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.627209617956176</v>
+        <v>-4.578809305610299</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.306709914888295</v>
+        <v>-2.282790284210485</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.405927395577663</v>
+        <v>-3.358012514264509</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.394760340824085</v>
+        <v>-5.343496384564432</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.40126096456963</v>
+        <v>-1.326797233888875</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.758296703183873</v>
+        <v>-2.656633407657687</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.499147574713199</v>
+        <v>-5.39714098695304</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.421300799123003</v>
+        <v>-2.297668103543884</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.334909061418415</v>
+        <v>-2.186264219572763</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.140718093731891</v>
+        <v>-3.96871933416535</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001467</t>
+          <t>X ≈ -0.001463</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4156848731159073</v>
+        <v>-0.4445452633676581</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.92555263195063</v>
+        <v>-5.336103043938252</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.093020467942559</v>
+        <v>-5.732878063825851</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.135536020986564</v>
+        <v>-4.364079741809448</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.843428408370784</v>
+        <v>-4.029153630359687</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.963446737453225</v>
+        <v>-4.171363703543285</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.979436394014357</v>
+        <v>-2.162713500476286</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4528359717179029</v>
+        <v>0.2704727088797796</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.8518368168097368</v>
+        <v>-1.008777899821787</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.115964001083626</v>
+        <v>-2.251043986736605</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.978859856957484</v>
+        <v>-4.115894688593841</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.871622209403796</v>
+        <v>-1.985013410508827</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.463065715798351</v>
+        <v>-1.553446977437581</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.421490975922886</v>
+        <v>1.008427494825646</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.0003411</t>
+          <t>X ≈ -0.0003381</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.788642026351184</v>
+        <v>-4.308911937817435</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.499111547355398</v>
+        <v>-4.979723127998724</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.153977813694958</v>
+        <v>-3.10789801255671</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.226369127553973</v>
+        <v>-5.699568067359714</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.94101611647644</v>
+        <v>-4.37585853505103</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.925350150693774</v>
+        <v>-3.653425633521117</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.38573904551032</v>
+        <v>-5.077863194887613</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.596854184126926</v>
+        <v>-5.543488052361425</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.576990538790135</v>
+        <v>-6.488175001325899</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-6.053953026789983</v>
+        <v>-5.951585105644909</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.633180347967119</v>
+        <v>-7.520837298243983</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.224241180521297</v>
+        <v>-6.103743874253972</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.188819106584475</v>
+        <v>-6.047482701026006</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.672688475141108</v>
+        <v>-4.434801475374272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007849</t>
+          <t>X ≈ 0.0007873</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.8004921752560392</v>
+        <v>0.5906846615520749</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2122546082694683</v>
+        <v>-0.6048352211335697</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.168085495931976</v>
+        <v>0.1634232445191728</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.08811896143949838</v>
+        <v>-0.483417040252391</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.309171546701492</v>
+        <v>0.9656353847687669</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.991366400841841</v>
+        <v>1.627390751700226</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4143437328057757</v>
+        <v>-0.764448143651741</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.815412056938534</v>
+        <v>-3.173256283711908</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.717432512483121</v>
+        <v>-2.044527763202986</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9173952659438953</v>
+        <v>0.6247247388616941</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.874985068575441</v>
+        <v>1.973333163696381</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.188960811470608</v>
+        <v>-1.079062459129524</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.651180779082509</v>
+        <v>2.64194071602396</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1641652336988599</v>
+        <v>0.1672501694789261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00191</t>
+          <t>X ≈ 0.001913</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.00062097334709</v>
+        <v>2.779034236385122</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.129980702950675</v>
+        <v>3.925805313990558</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.391520735268159</v>
+        <v>3.192129768364126</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.521578869401409</v>
+        <v>3.32265195168565</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.668050000698777</v>
+        <v>3.516542100513128</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.566451337497028</v>
+        <v>1.398149376792134</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.53938936109374</v>
+        <v>3.38910395994688</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.071732842284128</v>
+        <v>3.264451162075709</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.982032939533525</v>
+        <v>2.201706028010655</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.846448146340606</v>
+        <v>3.086570594048951</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.357282542342276</v>
+        <v>4.593436326347359</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.988390406940155</v>
+        <v>2.11230785318407</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.911738918119056</v>
+        <v>2.059615680044935</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.368832379867015</v>
+        <v>3.336057802334324</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003036</t>
+          <t>X ≈ 0.003038</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1672522133472611</v>
+        <v>0.1425372035854551</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7832002046216218</v>
+        <v>-0.7724643934737188</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.804700820360978</v>
+        <v>1.80413273971277</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.260848898471728</v>
+        <v>3.254482932547333</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2623054947473804</v>
+        <v>-0.2036402162051019</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2956872822443728</v>
+        <v>-0.2641593342909658</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.372492784532966</v>
+        <v>-2.310530433365123</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.18151568917807</v>
+        <v>-1.122473656606758</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.600425598383943</v>
+        <v>1.485806756118251</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4191148326691518</v>
+        <v>0.331523052267876</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.113285923160738</v>
+        <v>-1.198149549154024</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9131015000953155</v>
+        <v>0.8467721550982859</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.833441955840975</v>
+        <v>-1.866266566167532</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6110285647506615</v>
+        <v>-0.6238442207084134</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.0243679117479445</v>
+        <v>-0.04469435112805087</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8242084177123061</v>
+        <v>0.8293024216814402</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.858422934652971</v>
+        <v>-2.82479716787077</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.960532023600173</v>
+        <v>-3.923515236995833</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.659635282244018</v>
+        <v>1.71475039628632</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.547866581882957</v>
+        <v>1.576325787365683</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.999473991396762</v>
+        <v>-2.166963648748514</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.233806811699289</v>
+        <v>-1.405109267404733</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.528338251443458</v>
+        <v>-2.670579430444192</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.736063459464496</v>
+        <v>-1.859205618510217</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.706589701075913</v>
+        <v>-0.8371681139135063</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2613242520298371</v>
+        <v>-0.3691653109747932</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6836395140488776</v>
+        <v>-0.7643232375386759</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4579038638223452</v>
+        <v>-0.5152783755233088</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.421698992564615</v>
+        <v>2.906918003367331</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.432373591184003</v>
+        <v>3.922984134949061</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.471547010923302</v>
+        <v>4.830187482646885</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.534211914978876</v>
+        <v>1.478920991119381</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.498546905277713</v>
+        <v>4.470217661167737</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.551011516974135</v>
+        <v>6.930360370166319</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.586097055680298</v>
+        <v>5.807192059133328</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.557451213856616</v>
+        <v>5.777867304592547</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.498148306384593</v>
+        <v>5.742562096059771</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.283974875943741</v>
+        <v>9.098233496103106</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.956251873960312</v>
+        <v>9.77382766244844</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.42825372691133</v>
+        <v>10.26867562252075</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.068580542264741</v>
+        <v>5.943386691590113</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.539930227579042</v>
+        <v>4.445706662775784</v>
       </c>
     </row>
     <row r="27">
@@ -1667,202 +1667,202 @@
         <v>218</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.562429779083672</v>
+        <v>2.524812719950056</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.03766065210836445</v>
+        <v>0.04325062053512596</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.27138410445086</v>
+        <v>-1.257788628253081</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6924962831524866</v>
+        <v>0.6990332015050456</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.052377315028664</v>
+        <v>-2.996215959155691</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.214901322866808</v>
+        <v>-3.190892348813648</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.006886806116022</v>
+        <v>-0.9588247036138569</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.016128426107919</v>
+        <v>-0.9668289705557882</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6198358291500554</v>
+        <v>-0.5465240504383644</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.843649899600166</v>
+        <v>-2.744251334718363</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.04752265238907</v>
+        <v>-2.954027792060593</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.472214132035646</v>
+        <v>-3.354576651025987</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.980992932707061</v>
+        <v>-2.832303384929254</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9203948971594755</v>
+        <v>-0.7483961375927919</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.00754</t>
+          <t>X ≈ 0.007539</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.53606648755401</v>
+        <v>-0.948054032806354</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.165225262141909</v>
+        <v>-2.55248904247717</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.932664477508666</v>
+        <v>-3.229455531698328</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.165692902781366</v>
+        <v>-1.842924123754855</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.069803550670102</v>
+        <v>-2.346157118662887</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4801081352556764</v>
+        <v>-0.1642646533734862</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.836023653983794</v>
+        <v>6.135164183091014</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.089471254077857</v>
+        <v>4.397993843089857</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.034479991396438</v>
+        <v>4.36696603225456</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.256349220125628</v>
+        <v>1.627213884560604</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.046513010001412</v>
+        <v>1.159803797958681</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.727051855246366</v>
+        <v>1.854913210482813</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.323641271009656</v>
+        <v>2.09669795907822</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.549376921236188</v>
+        <v>2.345742821093587</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.008665</t>
+          <t>X ≈ 0.008664</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>147</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5803084592615448</v>
+        <v>0.8684988076050928</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.411299236946057</v>
+        <v>4.695038181739854</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.29543941681689</v>
+        <v>1.586593345521401</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.425664560405252</v>
+        <v>1.443739853295632</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8873750073095081</v>
+        <v>0.9477218649051338</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1757951807424689</v>
+        <v>-0.1518377717928558</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.621049757695758</v>
+        <v>-1.573038078705437</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6329700338916595</v>
+        <v>0.6822175962853763</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5719878773689118</v>
+        <v>0.6452449871486081</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.123429625256747</v>
+        <v>3.222776950551321</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.599000575840094</v>
+        <v>3.698908611858769</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.272834510508382</v>
+        <v>2.396531131536626</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.852683657194973</v>
+        <v>2.001373204972801</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.398147198577924</v>
+        <v>1.570145958144586</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.009789</t>
+          <t>X ≈ 0.009788</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>109</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.022200434204024</v>
+        <v>-2.034916155903524</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.468248912589033</v>
+        <v>-5.424889710461834</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.5589980512797581</v>
+        <v>0.5905417796431038</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.606654387528714</v>
+        <v>1.637723424130584</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.490383183056885</v>
+        <v>7.540101055218472</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.870326020031413</v>
+        <v>6.894283428981026</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.9507532754442</v>
+        <v>4.99876495443452</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1034713316452951</v>
+        <v>-0.05422376925157835</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7529777044924018</v>
+        <v>0.8262348142720981</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.57278367880469</v>
+        <v>3.672131004099263</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.368082520544611</v>
+        <v>3.467990556563286</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.6501670949181957</v>
+        <v>0.7738637159464403</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.652034590228638</v>
+        <v>6.800724138006466</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.877770240455227</v>
+        <v>7.04976900002189</v>
       </c>
     </row>
     <row r="31">
@@ -1875,150 +1875,150 @@
         <v>99</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.985966535584886</v>
+        <v>-2.534371125164384</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.473554442058379</v>
+        <v>2.897457899708463</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.098985077505368</v>
+        <v>4.494640001861427</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.209008200891681</v>
+        <v>2.6076118451684</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.690920667998064</v>
+        <v>4.114133134537177</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05210934277094736</v>
+        <v>-0.0281519338213343</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.146920712138133</v>
+        <v>-1.098909033147812</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.436515694580216</v>
+        <v>3.485763256973932</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.39573555825946</v>
+        <v>5.468992668039157</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.545816761929601</v>
+        <v>4.645164087224174</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.331014593568391</v>
+        <v>3.430922629587066</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.355291735822711</v>
+        <v>2.478988356850955</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.995746943115364</v>
+        <v>8.144436490893192</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.231583603442907</v>
+        <v>9.403582363009569</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01205</t>
+          <t>X ≈ 0.01204</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>74</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2217866721683421</v>
+        <v>0.2119789890259298</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.389399420895487</v>
+        <v>-1.350702092850554</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.621234599754885</v>
+        <v>3.653625539281919</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.102811094694658</v>
+        <v>5.139430986633272</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.213170190247517</v>
+        <v>3.261716110013289</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.159192868531335</v>
+        <v>2.183150277480948</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.777185211967883</v>
+        <v>4.825196890958203</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.310116568181087</v>
+        <v>4.359364130574804</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.210325047801113</v>
+        <v>-5.137067938021417</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.060243844130973</v>
+        <v>-5.9608965188364</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.562242299688535</v>
+        <v>-3.46233426366986</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.87921549868453</v>
+        <v>-4.755518877656286</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.073630701771407</v>
+        <v>-4.901631942204745</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.01317</t>
+          <t>X ≈ 0.01316</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>57</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.168206776483188</v>
+        <v>7.887834259837014</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.048248753594798</v>
+        <v>2.710305441690153</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.671021228488918</v>
+        <v>9.269926460649785</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.801246372077223</v>
+        <v>9.357020600281182</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.508570854069276</v>
+        <v>6.557116773835048</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.965984940857012</v>
+        <v>-1.942027531907399</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2963093352109283</v>
+        <v>-0.2482976562206076</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-7.780921838646798</v>
+        <v>-7.731674276253081</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-13.10506188990642</v>
+        <v>-13.03180478012672</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-10.44620875641169</v>
+        <v>-10.34686143111711</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.387752019935057</v>
+        <v>-5.287843983916382</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.598987902667425</v>
+        <v>-3.47529128163918</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-5.773524720893143</v>
+        <v>-5.624835173115315</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.793403105754336</v>
+        <v>-3.621404346187674</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>9.544261512765452</v>
+        <v>9.543074726320796</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.69494467346494</v>
+        <v>13.69479128346062</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.82516981705331</v>
+        <v>13.82467532467531</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.741425718503081</v>
+        <v>8.789971638268852</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.58425429359269</v>
+        <v>13.60821170254231</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.59045302523558</v>
+        <v>22.6384647042259</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.57792983599436</v>
+        <v>17.62717739838808</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.97149313401702</v>
+        <v>13.04475024379672</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.12157433768715</v>
+        <v>12.22092166298172</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.46232772488156</v>
+        <v>16.56223576090024</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.04216042269133</v>
+        <v>21.16585704371958</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>20.62200956937798</v>
+        <v>20.77069911715581</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.84774521960455</v>
+        <v>21.01974397917122</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1041 +2210,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01779</t>
+          <t>X &gt; -0.01778</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2035654600270576</v>
+        <v>0.2038246054308672</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2482607994032904</v>
+        <v>0.2476257390156107</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2592633569889458</v>
+        <v>0.2585699705269988</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2557166990231678</v>
+        <v>0.2550421196127033</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2461663766179711</v>
+        <v>0.2441611100794745</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.3607080803557849</v>
+        <v>0.359074059279834</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3385948907357132</v>
+        <v>0.3363544736142643</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3025235134367463</v>
+        <v>0.3003455234298116</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3534185041516906</v>
+        <v>0.350438186427354</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3279625440753762</v>
+        <v>0.3243276909160784</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2599997014672368</v>
+        <v>0.2565316610784549</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.4066012915570454</v>
+        <v>0.4020780426275721</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4429631424830234</v>
+        <v>0.4376481563461496</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4859869581905727</v>
+        <v>0.4799085386734916</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01667</t>
+          <t>X &gt; -0.01665</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4041</v>
+        <v>4052</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1091185032594311</v>
+        <v>0.1098143743750057</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2626967907862223</v>
+        <v>0.2620260505870817</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.202168939820524</v>
+        <v>0.2016268058019435</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2471531657214356</v>
+        <v>0.2465006682141109</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2902472673246308</v>
+        <v>0.287811400083001</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.4283684407446486</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3819550015202182</v>
+        <v>0.3792875670000413</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2744278030631193</v>
+        <v>0.2720091560833069</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3260071321296465</v>
+        <v>0.3226313471646378</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.355083720763929</v>
+        <v>0.3507405620314117</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2385169165009842</v>
+        <v>0.2344698153784037</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4352753463529382</v>
+        <v>0.4298835943766761</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4497276207476943</v>
+        <v>0.4434443339424803</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4916227476691262</v>
+        <v>0.4844303293461749</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01554</t>
+          <t>X &gt; -0.01553</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1166479764256323</v>
+        <v>0.105806846077563</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3832832568095768</v>
+        <v>0.3709968042428713</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3004928184311595</v>
+        <v>0.2884630545077584</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3448441725485765</v>
+        <v>0.3326834455866674</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2431561353865277</v>
+        <v>0.2541292230518977</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3551489042085763</v>
+        <v>0.3668106011610917</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.358801181933309</v>
+        <v>0.3694622887124979</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2042427660921433</v>
+        <v>0.1905156994312946</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2566737068688312</v>
+        <v>0.24181404955619</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3174342824260421</v>
+        <v>0.3263798231118784</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1267818852240481</v>
+        <v>0.1362307442911543</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3496923722971204</v>
+        <v>0.3575753204702394</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3425508082438355</v>
+        <v>0.3495013147095634</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.4079356526129132</v>
+        <v>0.4136833731105725</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01441</t>
+          <t>X &gt; -0.0144</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3973</v>
+        <v>3984</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05295250935526497</v>
+        <v>0.05431149260113699</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3370070357493731</v>
+        <v>0.3361405193865963</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2069015920483892</v>
+        <v>0.2063398100279414</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2253250221294394</v>
+        <v>0.2247299520709518</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.228115823977717</v>
+        <v>0.2249829079908636</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3383818540503398</v>
+        <v>0.336213160002707</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3428513806490656</v>
+        <v>0.3394282358083842</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1409310468970446</v>
+        <v>0.1379999092105848</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2446774660248963</v>
+        <v>0.2402196027155767</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.313907526248677</v>
+        <v>0.3079099004213433</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1736867883532653</v>
+        <v>0.1680455518115735</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3480495021653809</v>
+        <v>0.3406962536817844</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3447528552818113</v>
+        <v>0.3361148808149892</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.4086449290066199</v>
+        <v>0.3986231321467244</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01329</t>
+          <t>X &gt; -0.01328</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3917</v>
+        <v>3928</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0127226463104364</v>
+        <v>-0.0107461816492247</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3237797801941369</v>
+        <v>0.3229547447795014</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2483607075327185</v>
+        <v>0.2476773412971909</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2142709120367741</v>
+        <v>0.2137052891242774</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2757192395515773</v>
+        <v>0.2717182381256933</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3578501245133907</v>
+        <v>0.3552553093420343</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4145657117336512</v>
+        <v>0.410210112566034</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2419392907251918</v>
+        <v>0.2379829629302961</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4755495059979395</v>
+        <v>0.4693393846330096</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.481454702158203</v>
+        <v>0.4734880182947947</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4187284669965479</v>
+        <v>0.4108979102491972</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5951539971190059</v>
+        <v>0.5852417302798969</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5723552930774645</v>
+        <v>0.5608377136064462</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.6084619090932222</v>
+        <v>0.5952855455477746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01216</t>
+          <t>X &gt; -0.01215</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3852</v>
+        <v>3862</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1070756878921415</v>
+        <v>0.1092430138226916</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4509990930728023</v>
+        <v>0.4498189887697563</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3551772425530473</v>
+        <v>0.3541814672505126</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2523625104293359</v>
+        <v>0.2657910271546555</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.3239173009946725</v>
+        <v>0.3331481724037957</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4801563190284242</v>
+        <v>0.4909930039282813</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5392857421429795</v>
+        <v>0.5479550587925601</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3457322772027069</v>
+        <v>0.3549201830077919</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5324802412836362</v>
+        <v>0.5391668693227416</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5009594753710616</v>
+        <v>0.5057356591252855</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3887514956632714</v>
+        <v>0.3938246118939688</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4897237571255175</v>
+        <v>0.4925086529799501</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5514624160382056</v>
+        <v>0.5520748731626881</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6362848212282373</v>
+        <v>0.6346396997116486</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01104</t>
+          <t>X &gt; -0.01103</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3780</v>
+        <v>3790</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1562147711534081</v>
+        <v>0.1588337444004253</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4053919412923506</v>
+        <v>0.404343914786196</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4735486552351773</v>
+        <v>0.4721943592062559</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2607658832562549</v>
+        <v>0.2744360902255565</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.370303570658848</v>
+        <v>0.3786672280173562</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4974730705918589</v>
+        <v>0.5080154269906032</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5329356812118249</v>
+        <v>0.5408756985516234</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3974082973111663</v>
+        <v>0.405700245404077</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4832020327800919</v>
+        <v>0.4887555138889539</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.546521483564554</v>
+        <v>0.5493828696717316</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4625199724964517</v>
+        <v>0.4655984145924066</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5383384910534943</v>
+        <v>0.5386993912455367</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5299223389675589</v>
+        <v>0.527779283099072</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6385100103693091</v>
+        <v>0.6335602420639574</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.009911</t>
+          <t>X &gt; -0.009903</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3701</v>
+        <v>3710</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1322305211897827</v>
+        <v>0.1228811896213529</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5023468119986916</v>
+        <v>0.5156871716556282</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5535577584931346</v>
+        <v>0.5398548220725701</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.306424411515458</v>
+        <v>0.3080897322628928</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5377932765314597</v>
+        <v>0.5328441503721351</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7152732207281502</v>
+        <v>0.7129149089404478</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6724600389933926</v>
+        <v>0.6671367856429313</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5441271572915056</v>
+        <v>0.5511425613198639</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6601202963284081</v>
+        <v>0.6637395989906594</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7162140392383236</v>
+        <v>0.7165402070655631</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5385107211509137</v>
+        <v>0.5545967529918698</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.64223898307241</v>
+        <v>0.6549832192682317</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4805626856296499</v>
+        <v>0.4906961774924028</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6947153259639762</v>
+        <v>0.7011946040180277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.008785</t>
+          <t>X &gt; -0.008777</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3595</v>
+        <v>3602</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2382848573679794</v>
+        <v>0.2161544358381775</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6400655144811935</v>
+        <v>0.6534589449253332</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8712608614413355</v>
+        <v>0.8562732123844228</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5295259828198127</v>
+        <v>0.5306998457095347</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7963447029056852</v>
+        <v>0.8045775309910894</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9425638540683465</v>
+        <v>0.9542405697682028</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9288368636194804</v>
+        <v>0.9366908683057744</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7550750025810302</v>
+        <v>0.7757361567029264</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6818372645946269</v>
+        <v>0.698806750085005</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7370872651267035</v>
+        <v>0.7501406414519778</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6157889425629293</v>
+        <v>0.6449491640019502</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6779680401503896</v>
+        <v>0.7188789385839343</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5517294601657241</v>
+        <v>0.5892846393216828</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7377439552221645</v>
+        <v>0.7708923310968814</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.007659</t>
+          <t>X &gt; -0.007652</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3492</v>
+        <v>3498</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2468760288772387</v>
+        <v>0.2399594204820588</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3936121621160993</v>
+        <v>0.4236674877912989</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9575391809865863</v>
+        <v>0.9576709351658295</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.744809194537801</v>
+        <v>0.7611919019104647</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.8352707131768824</v>
+        <v>0.8581145620877635</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.9484624125178129</v>
+        <v>0.9756089272862027</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9368278400119365</v>
+        <v>0.9593447374347619</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8575220972799755</v>
+        <v>0.8930553560468439</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5836663685078562</v>
+        <v>0.6151444513590789</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.722812824443686</v>
+        <v>0.749554651923134</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6039731430008999</v>
+        <v>0.6473023652470076</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.8386947412634882</v>
+        <v>0.8931297709923598</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6639115551677506</v>
+        <v>0.7143193722936516</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.96333409807999</v>
+        <v>1.008308873396459</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006533</t>
+          <t>X &gt; -0.006527</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3385</v>
+        <v>3391</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4359961674621147</v>
+        <v>0.4293355590048407</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4024454743976946</v>
+        <v>0.4040655873116634</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.026098189759992</v>
+        <v>0.9966543718571046</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8615120125936357</v>
+        <v>0.8487394957983128</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.207656421762096</v>
+        <v>1.199503853626311</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.315146226784854</v>
+        <v>1.312208706127322</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.187932242183876</v>
+        <v>1.209128659052418</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.002914411760869</v>
+        <v>1.03767329048538</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9289901824231706</v>
+        <v>0.9583384224025764</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8928119574633229</v>
+        <v>0.9168648950074498</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7766847584591119</v>
+        <v>0.8178740530735524</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8110629108144352</v>
+        <v>0.8633626032941564</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8212255925751109</v>
+        <v>0.8682548632964711</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.063939660318901</v>
+        <v>1.104728295945534</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005407</t>
+          <t>X &gt; -0.005402</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3258</v>
+        <v>3264</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4116459529367233</v>
+        <v>0.375384358319117</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1944869762181014</v>
+        <v>0.1967874258350193</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9495736585686814</v>
+        <v>0.9192040118440516</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8654037026164616</v>
+        <v>0.8826982672078927</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.24595029040897</v>
+        <v>1.235515092369766</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.31542630785296</v>
+        <v>1.342015654628156</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.155911471172168</v>
+        <v>1.176134985015509</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8592407997087506</v>
+        <v>0.8937884631642703</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.754103041741935</v>
+        <v>0.7821734201920734</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6882224135377086</v>
+        <v>0.7098501151904912</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5141961019032806</v>
+        <v>0.5536652068751025</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7326233340132049</v>
+        <v>0.78229082426855</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.759530839148411</v>
+        <v>0.802719164489794</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9415004514813035</v>
+        <v>0.9774088633066498</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004281</t>
+          <t>X &gt; -0.004276</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3103</v>
+        <v>3110</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2504464373319735</v>
+        <v>0.2293947435205723</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.006258532139526096</v>
+        <v>0.02398119569249957</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7221297070808603</v>
+        <v>0.705280793950152</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7558918281611824</v>
+        <v>0.7566756744377798</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.085769477637847</v>
+        <v>1.086898572783987</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9186792767793506</v>
+        <v>0.9284788591906263</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8196562544388613</v>
+        <v>0.8214498833600459</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5313780614091073</v>
+        <v>0.5481716801012197</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4561269805311099</v>
+        <v>0.4648582257024643</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.525907524629055</v>
+        <v>0.5259371356272737</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.417824723856782</v>
+        <v>0.4363122144819513</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.6454395911879587</v>
+        <v>0.6733354265193583</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6302101317022561</v>
+        <v>0.6500129887551225</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.971086267856947</v>
+        <v>0.9817433945468039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003156</t>
+          <t>X &gt; -0.003151</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2943</v>
+        <v>2949</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1952357309832706</v>
+        <v>0.1766066610880088</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2623539929724643</v>
+        <v>0.2831896300044789</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7334654746976241</v>
+        <v>0.7530001469433358</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5247075674385329</v>
+        <v>0.5295666457316699</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8338756414614821</v>
+        <v>0.8369638882381025</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7093198011607669</v>
+        <v>0.7225018117563025</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6094489546793298</v>
+        <v>0.6128599771994345</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3647392261291671</v>
+        <v>0.3839940414606318</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3904896161499636</v>
+        <v>0.4147262393651374</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6120821320998857</v>
+        <v>0.6256256619966223</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5092485459958951</v>
+        <v>0.5422801067982022</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5436266983512184</v>
+        <v>0.5857763314803393</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6522714270854948</v>
+        <v>0.6844125223946378</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.033393753876908</v>
+        <v>1.054578591828779</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.00203</t>
+          <t>X &gt; -0.002026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2746</v>
+        <v>2752</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5136393233676415</v>
+        <v>0.5311626139254741</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2651963513473561</v>
+        <v>0.2513888596892357</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7256219511455129</v>
+        <v>0.7103653508275301</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7468750642216975</v>
+        <v>0.7515527950310528</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.225657795906244</v>
+        <v>1.224648233873324</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9256919257280245</v>
+        <v>0.9376335497306698</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8975149200837862</v>
+        <v>0.8971121141247309</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7779298359943496</v>
+        <v>0.7939924476840758</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5190310817004899</v>
+        <v>0.5393919821816624</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8538755154032032</v>
+        <v>0.8605838875496374</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9402951722812887</v>
+        <v>0.9674494220122227</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7563327132829016</v>
+        <v>0.7921856896561295</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8665738874770739</v>
+        <v>0.8899079141706423</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.40458823092677</v>
+        <v>1.414167869234603</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.000904</t>
+          <t>X &gt; -0.0009007</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2505</v>
+        <v>2511</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6030473598357204</v>
+        <v>0.6248088100336489</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7645857744909961</v>
+        <v>0.7876634709095498</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.285419485277345</v>
+        <v>1.328773022245876</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.216600042878461</v>
+        <v>1.24253943038692</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.713342336916511</v>
+        <v>1.728896043224246</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.396064148413323</v>
+        <v>1.42798334584338</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.174299457687646</v>
+        <v>1.190787133287948</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8092063315195546</v>
+        <v>0.8442386671392015</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6509189713376102</v>
+        <v>0.6879817637678087</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.139596602618099</v>
+        <v>1.159230768355286</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.413555197050364</v>
+        <v>1.455337088541924</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.009161909437594</v>
+        <v>1.058734866533776</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.09070288723332</v>
+        <v>1.124415492377565</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.499169643484031</v>
+        <v>1.453109896408066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002218</t>
+          <t>X &gt; 0.0002245</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2287</v>
+        <v>2291</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.116990641947112</v>
+        <v>1.098583827286923</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.361650057902686</v>
+        <v>1.341493698652819</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.708588969831766</v>
+        <v>1.754817381764248</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.92607414832414</v>
+        <v>1.909175680716146</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.347644979172607</v>
+        <v>2.315123021495985</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.903308712123575</v>
+        <v>1.91594055905167</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.799611391967119</v>
+        <v>1.79275268204335</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.419840871270729</v>
+        <v>1.457638875908373</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.33989329281021</v>
+        <v>1.377093282022116</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.825295692784678</v>
+        <v>1.842067735740727</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.275902529282021</v>
+        <v>2.317300582689846</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.698659886530308</v>
+        <v>1.746532912353629</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.7845969819654</v>
+        <v>1.813118068784718</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.992158305425562</v>
+        <v>2.01851386925491</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001348</t>
+          <t>X &gt; 0.00135</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.157235395227694</v>
+        <v>1.162757910666393</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.561781848869863</v>
+        <v>1.587416280946385</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.904473590958489</v>
+        <v>1.955893238830114</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.182191359915578</v>
+        <v>2.211484593837532</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.479693350576028</v>
+        <v>2.485633504602625</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.892111627998723</v>
+        <v>1.952399408849764</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.081129589202902</v>
+        <v>2.115860161002857</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.958379686193346</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.728651330151607</v>
+        <v>1.809421998159202</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.940740892451956</v>
+        <v>1.995881477234292</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.3268816839702</v>
+        <v>2.360761559425995</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.065838861436298</v>
+        <v>2.103552583185085</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.674405449360073</v>
+        <v>1.708394656621259</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.224599021298147</v>
+        <v>2.252424769374095</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002473</t>
+          <t>X &gt; 0.002475</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.848590284046594</v>
+        <v>0.8918321430947174</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.131778473416745</v>
+        <v>1.19544751076905</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.655491589235758</v>
+        <v>1.748671042145894</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.957932576681756</v>
+        <v>2.025226919617296</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.280722242874234</v>
+        <v>2.312829078652065</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.946638178364658</v>
+        <v>2.045304695509252</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.836967567557195</v>
+        <v>1.902434679205115</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.771966700910021</v>
+        <v>1.837978065610756</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.686226676336787</v>
+        <v>1.743666006932678</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.789094856271525</v>
+        <v>1.813056435839407</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.986923887775561</v>
+        <v>1.986512976222187</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.078806352954345</v>
+        <v>2.102084994872968</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.634667797226086</v>
+        <v>1.649521787023254</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.033015645381276</v>
+        <v>2.070782492896264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003599</t>
+          <t>X &gt; 0.0036</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.9913061916878689</v>
+        <v>1.048975942908463</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.532897876401819</v>
+        <v>1.608162368464413</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.624237602757894</v>
+        <v>1.737039491683952</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.685018301901806</v>
+        <v>1.767424616905586</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.813395415472776</v>
+        <v>2.840588611323504</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.41632500066342</v>
+        <v>2.529650623981247</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.718698650354092</v>
+        <v>2.785987084758048</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.39061541309966</v>
+        <v>2.45885057957581</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.704198927181473</v>
+        <v>1.797744822034026</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.076056573115167</v>
+        <v>2.123766909338443</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.636306736134529</v>
+        <v>2.654407478071917</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.32297974245369</v>
+        <v>2.365351993214595</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.361112498460038</v>
+        <v>2.386860733317434</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.58684814868657</v>
+        <v>2.635905595332801</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.198013735351935</v>
+        <v>1.272099313932628</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.677128645632592</v>
+        <v>1.767060217139203</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.536537862884231</v>
+        <v>2.667715198148287</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.833987086740152</v>
+        <v>2.928452480076125</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.048205894848479</v>
+        <v>3.070274668571891</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.593071563279544</v>
+        <v>2.724141644160348</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.678929765886295</v>
+        <v>3.796455294603859</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.128249081965777</v>
+        <v>3.247150080130368</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.565594684640324</v>
+        <v>2.70934274645267</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.851890047082385</v>
+        <v>2.936346588932992</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.316644955767799</v>
+        <v>3.366735608878315</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.848931057913916</v>
+        <v>2.923230105440531</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.980773083920397</v>
+        <v>3.029744419679382</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.206508734146929</v>
+        <v>3.278789281694749</v>
       </c>
     </row>
     <row r="27">
@@ -3306,205 +3306,205 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.673168767811049</v>
+        <v>0.8849499035080797</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.026822385191885</v>
+        <v>1.256505328640287</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.079827629185559</v>
+        <v>2.155609558903009</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.14076631982666</v>
+        <v>3.271723122238576</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.705889383070158</v>
+        <v>2.738747320790665</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.658899400295731</v>
+        <v>1.72804641328613</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.228790902456659</v>
+        <v>3.320282886044147</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.554897025991536</v>
+        <v>2.647838555412861</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.873439171433596</v>
+        <v>1.991031235532262</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.333758224121318</v>
+        <v>1.47712001008918</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.749532763896283</v>
+        <v>1.849440799914959</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.060022601877257</v>
+        <v>1.183719222905502</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.251973808037874</v>
+        <v>2.339750541429574</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.891788133212643</v>
+        <v>3.002445868801715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.006977</t>
+          <t>X &gt; 0.006976</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1225552645257224</v>
+        <v>0.4076600584021364</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.315107489218903</v>
+        <v>1.609628861840449</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.05651767989778</v>
+        <v>3.149095279597312</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.854299565809242</v>
+        <v>4.020516717325229</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.384100800430502</v>
+        <v>4.407935565154219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.079338648490157</v>
+        <v>3.159726854057482</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.463253122334798</v>
+        <v>4.565737431498682</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.595650433154212</v>
+        <v>3.699904671115341</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.600088837379097</v>
+        <v>2.729598728645215</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.551238131836953</v>
+        <v>2.705770147830229</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.147605064364477</v>
+        <v>3.247513100383152</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.380915125932084</v>
+        <v>2.504611746960329</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.777089783281724</v>
+        <v>3.845101350436551</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.002825433508256</v>
+        <v>4.094146212451918</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.008103</t>
+          <t>X &gt; 0.008101</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>592</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5596245100061878</v>
+        <v>0.7671990994827667</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.495735714239657</v>
+        <v>2.71343377903279</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.634748113268401</v>
+        <v>4.840704194079436</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.440648932532447</v>
+        <v>5.575517075517077</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.084791811869174</v>
+        <v>6.199139199207067</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.017300976639405</v>
+        <v>4.041258385589018</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.101509536292149</v>
+        <v>4.149521215282469</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.465521973586497</v>
+        <v>3.514769535980214</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.222107384631286</v>
+        <v>2.295364494410983</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.892458858571686</v>
+        <v>2.99180618386626</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.701271213825017</v>
+        <v>3.801179249843692</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.553216933747905</v>
+        <v>2.676913554776149</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.160093107461527</v>
+        <v>4.308782655239355</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.38582875768806</v>
+        <v>4.557827517254722</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.009228</t>
+          <t>X &gt; 0.009226</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>445</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.552791834634192</v>
+        <v>0.7337360498333751</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.862954056177095</v>
+        <v>2.058836369599227</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.73784559277037</v>
+        <v>5.91565766540085</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.766947140853119</v>
+        <v>6.940396292745284</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.801691295622597</v>
+        <v>7.933877060201191</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.991883055879157</v>
+        <v>6.039894734869478</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.40121890647444</v>
+        <v>4.450466468868157</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.767203042086493</v>
+        <v>2.840460151866189</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.816160650251007</v>
+        <v>2.91550797554558</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.645837644346138</v>
+        <v>2.769534265374382</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.922316004515878</v>
+        <v>5.071005552293705</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.372770755866007</v>
+        <v>5.544769515432669</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>336</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.388131588513261</v>
+        <v>1.631900009432542</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.486592746761893</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.643150616435356</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.440970682854186</v>
+        <v>8.66060862214708</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.902681129758491</v>
+        <v>8.061619871341414</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.329630514413132</v>
+        <v>6.377642193403453</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.862561870626394</v>
+        <v>5.91180943302011</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.420627333151238</v>
+        <v>3.493884442930934</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.570708536821378</v>
+        <v>2.670055862115952</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.854102616656412</v>
+        <v>3.954010652675088</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.293242673773648</v>
+        <v>3.416939294801892</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.36118705855548</v>
+        <v>4.509876606333307</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.884541756401056</v>
+        <v>5.056540515967718</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>237</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.215286501111216</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.979627834207726</v>
+        <v>5.150408568948762</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.804265732153112</v>
+        <v>8.958351252902958</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>11.04419551709169</v>
+        <v>11.18907563025209</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.662024107455899</v>
+        <v>9.710570027221671</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.005811639200701</v>
+        <v>7.029769048150314</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.452746849554785</v>
+        <v>9.500758528545106</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.875973564417826</v>
+        <v>6.925221126811543</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.595582125194639</v>
+        <v>2.668839234974335</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.745663328864779</v>
+        <v>1.845010654159353</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.072607740224825</v>
+        <v>4.1725157762435</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.685044964310116</v>
+        <v>3.80874158533836</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.84295318272666</v>
+        <v>2.991642730504488</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.068688832953193</v>
+        <v>3.240687592519855</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01261</t>
+          <t>X &gt; 0.0126</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>163</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.574298693392031</v>
+        <v>4.806961345844719</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.871088060450894</v>
+        <v>8.101833041176675</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.15729827078788</v>
+        <v>11.36663163822783</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.74151114443759</v>
+        <v>13.93554006968641</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.58972465882656</v>
+        <v>12.63827057859233</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.206117093369627</v>
+        <v>9.230074502319241</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.5753944641648</v>
+        <v>11.62340614315512</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.040841157801381</v>
+        <v>8.090088720195098</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.139368203732595</v>
+        <v>6.212625313512291</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.289449407402735</v>
+        <v>5.388796732697308</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.538735979203892</v>
+        <v>7.638644015222567</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.573114131559215</v>
+        <v>7.69681075258746</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.152963278245807</v>
+        <v>7.301652826023634</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.765201995957</v>
+        <v>6.937200755523662</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.179461327956211</v>
+        <v>3.15026553360358</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>11.00223749904333</v>
+        <v>11.00105071259868</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.49425856711847</v>
+        <v>12.49410517711415</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.39806861636722</v>
+        <v>16.39757412398922</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.85977906327152</v>
+        <v>15.9083249830373</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.21375686649151</v>
+        <v>15.23771427544112</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17.95923518647062</v>
+        <v>18.00724686546094</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.54877031626879</v>
+        <v>16.59801787866251</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.48778815974602</v>
+        <v>16.56104526952571</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.75107691058597</v>
+        <v>13.85042423588054</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.48977197874088</v>
+        <v>14.58968001475955</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.5807539046811</v>
+        <v>13.70445052570934</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.10399927778279</v>
+        <v>14.25268882556062</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.44294247517913</v>
+        <v>12.61494123474579</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01486</t>
+          <t>X &gt; 0.01485</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>11.3840883525923</v>
+        <v>11.38290156614764</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>17.07192306380657</v>
+        <v>17.07142857142857</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>17.72410970118707</v>
+        <v>17.77265562095284</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>15.64053134986976</v>
+        <v>15.66448875881937</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>16.79430886007012</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.32847609968677</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.40872257124647</v>
+        <v>17.48197968102617</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.17785139396422</v>
+        <v>14.27719871925879</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.97315023570403</v>
+        <v>14.0730582717227</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.62657600710698</v>
+        <v>11.75027262813523</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>12.39690134426976</v>
+        <v>12.54559089204759</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1041 +3904,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01779</t>
+          <t>X &lt; -0.01778</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.433296982915309</v>
+        <v>-8.46249277726794</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.85400688550294</v>
+        <v>-8.855193671947596</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.62973065121037</v>
+        <v>-11.62988404121469</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-10.30902931714581</v>
+        <v>-10.30952380952382</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.656842679765312</v>
+        <v>-9.60829675999954</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.93089722155879</v>
+        <v>-12.90693981260918</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.444179009396393</v>
+        <v>-9.396167330406072</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.530295272230759</v>
+        <v>-7.481047709837043</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.591277428753536</v>
+        <v>-7.518020318973839</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.250720034607198</v>
+        <v>-7.151372709312625</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.074468811915011</v>
+        <v>-4.974560775896336</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.99247161194064</v>
+        <v>-10.86877499091239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.60309865573024</v>
+        <v>-12.45440910795242</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-14.75831538645608</v>
+        <v>-14.58631662688942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01667</t>
+          <t>X &lt; -0.01665</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.939631626864625</v>
+        <v>-2.968827421217256</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.303111297910107</v>
+        <v>-7.304298084354762</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.780451490004594</v>
+        <v>-6.780604880008916</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.567657539076784</v>
+        <v>-7.568152031454787</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.023378284833029</v>
+        <v>-8.974832365067257</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-12.39572902584014</v>
+        <v>-12.37177161689053</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.810714614464111</v>
+        <v>-8.76270293547379</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.690627294948101</v>
+        <v>-4.641379732554384</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.751609451470877</v>
+        <v>-4.678352341691181</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.518959440461281</v>
+        <v>-6.419612115166707</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.053935828079268</v>
+        <v>-2.954027792060593</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.441576024347803</v>
+        <v>-9.317879403319559</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.861726877661212</v>
+        <v>-9.713037329883385</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.47085361275578</v>
+        <v>-11.29885485318912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01554</t>
+          <t>X &lt; -0.01553</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.155501895808975</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.092102123598181</v>
+        <v>-8.70321798805702</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.058302079781789</v>
+        <v>-7.678516260059666</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.642362650479143</v>
+        <v>-8.257852077001019</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.609223632146261</v>
+        <v>-5.910221785328822</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.454706745368327</v>
+        <v>-7.765095840977978</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.110845676063065</v>
+        <v>-6.407312213891387</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.199386109026499</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.236358718163295</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.917386701273863</v>
+        <v>-4.187846873446368</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.5725516861097475</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.801995421464454</v>
+        <v>-5.043040441773591</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.507860560492141</v>
+        <v>-4.728978510181392</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.607593222634108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01441</t>
+          <t>X &lt; -0.0144</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>177</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5035149005908508</v>
+        <v>-0.5327106949434821</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.069503253541683</v>
+        <v>-6.070690039986339</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.204387632647006</v>
+        <v>-4.204541022651327</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.074162489058644</v>
+        <v>-4.074656981436647</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.047480290741909</v>
+        <v>-3.998934370976137</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.445021515344109</v>
+        <v>-5.421064106394496</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.399788371785419</v>
+        <v>-4.351776692795099</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2178887471397033</v>
+        <v>0.26713630953342</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.973036912207931</v>
+        <v>-0.8997798024282346</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.952899211362649</v>
+        <v>-2.853551886068075</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3327416125606959</v>
+        <v>-0.2328335765420206</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.68819396867994</v>
+        <v>-3.564497347651695</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.543373070580927</v>
+        <v>-3.394683522803099</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.012552674591674</v>
+        <v>-4.840553915025012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01329</t>
+          <t>X &lt; -0.01328</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>233</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.7379680896373202</v>
+        <v>0.7087722952846889</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.306694398276292</v>
+        <v>-4.307881184720948</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.843096684318887</v>
+        <v>-3.843250074323208</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.854502442018081</v>
+        <v>-2.854996934396084</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.821976544469997</v>
+        <v>-3.773430624704226</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.382971613547348</v>
+        <v>-4.359014204597734</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.467681972813516</v>
+        <v>-4.419670293823195</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.501274221750478</v>
+        <v>-1.452026659356761</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.566548223766816</v>
+        <v>-4.493291113987119</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.987282470740453</v>
+        <v>-4.88793514544588</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.333614530288202</v>
+        <v>-4.233706494269526</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.874343674070211</v>
+        <v>-6.750647053041966</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.436125428671168</v>
+        <v>-6.287435880893341</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-7.068758877157087</v>
+        <v>-6.896760117590425</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01216</t>
+          <t>X &lt; -0.01215</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9758993081263299</v>
+        <v>-1.005095102478961</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.928222524935975</v>
+        <v>-4.929409311380631</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.319649428085661</v>
+        <v>-4.319802818089983</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.678796015771567</v>
+        <v>-2.852126134734839</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.552656038665923</v>
+        <v>-3.675823436221869</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.93313435802412</v>
+        <v>-5.075278720078529</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.017844717290288</v>
+        <v>-5.13593480930399</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.464779132889113</v>
+        <v>-2.59173412487128</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.203613638405173</v>
+        <v>-4.300947536683658</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.046821025339064</v>
+        <v>-4.121431635893295</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.909240304404626</v>
+        <v>-2.987779441288914</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.881573561445272</v>
+        <v>-3.932957185529375</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.637294884557342</v>
+        <v>-4.662563272628319</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.753841113525439</v>
+        <v>-5.751311052753415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01104</t>
+          <t>X &lt; -0.01103</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.267978025143513</v>
+        <v>-1.297173819496145</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.418247676158835</v>
+        <v>-3.41943446260349</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.621644397841095</v>
+        <v>-4.621797787845416</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.194486202602697</v>
+        <v>-2.335579514824808</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.273316296238939</v>
+        <v>-3.363912213728206</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.057023347684932</v>
+        <v>-4.169293810812242</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.87146343668082</v>
+        <v>-3.960408121061967</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.446640188575678</v>
+        <v>-2.539448428615117</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.777892615368721</v>
+        <v>-2.845962816727649</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.62781141169858</v>
+        <v>-3.669791397542632</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.021701759147959</v>
+        <v>-3.065306508151494</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.527864147333183</v>
+        <v>-3.546223328738094</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.407474460106044</v>
+        <v>-3.402297697350427</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.533090161230859</v>
+        <v>-4.500961730213774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.009911</t>
+          <t>X &lt; -0.009903</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8179448553680615</v>
+        <v>-0.7402003204622005</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.537778398542756</v>
+        <v>-3.650811033936641</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.376008763342135</v>
+        <v>-4.265787960304451</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.13442614254263</v>
+        <v>-2.144753476611882</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.006049028971667</v>
+        <v>-3.961436245882389</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.042008332669909</v>
+        <v>-5.016084355382048</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.237829803047184</v>
+        <v>-4.191784692395117</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.149342891278373</v>
+        <v>-3.215394663696188</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.654769492245592</v>
+        <v>-3.695826252877332</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.28246606635323</v>
+        <v>-4.297925343670144</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.035546338694097</v>
+        <v>-3.171688851073192</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.669319634000246</v>
+        <v>-3.778710583774817</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.307733293549731</v>
+        <v>-2.40003259016126</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.086451986307608</v>
+        <v>-4.146553138345446</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.008785</t>
+          <t>X &lt; -0.008777</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.318125332859928</v>
+        <v>-1.173213429165052</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.644874932184948</v>
+        <v>-3.736146052899983</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.470773329462347</v>
+        <v>-5.379884041214687</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.102168078026509</v>
+        <v>-3.107142857142868</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.805171311038293</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.405463349625826</v>
+        <v>-5.466463622132999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.951574067958418</v>
+        <v>-4.991405425644167</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.802843788944443</v>
+        <v>-3.937304631210232</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.966159877244593</v>
+        <v>-3.079822857520561</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.457012246285409</v>
+        <v>-3.545869685204948</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.847678815340842</v>
+        <v>-3.034446626479856</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.077413696882722</v>
+        <v>-3.334061642245558</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.23630328893487</v>
+        <v>-2.476983432852322</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.452009080149779</v>
+        <v>-3.659065583359315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.007659</t>
+          <t>X &lt; -0.007652</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.12139941422015</v>
+        <v>-1.08154039631556</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.675183694595155</v>
+        <v>-1.834252765464527</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.940045713791285</v>
+        <v>-4.938834127273203</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.67586167792674</v>
+        <v>-3.754733218588648</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.137362160284795</v>
+        <v>-4.243982359540567</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.446048736710317</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.076213641431025</v>
+        <v>-4.182455339585658</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.634191376126857</v>
+        <v>-3.818044046833379</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.876991714467813</v>
+        <v>-2.045061904838946</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.726910510797673</v>
+        <v>-2.868890485653928</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.243700692831268</v>
+        <v>-2.469712682812947</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.343028856114906</v>
+        <v>-3.618182446202198</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.39539855441312</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.993371110873511</v>
+        <v>-4.21678419853346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006533</t>
+          <t>X &lt; -0.006527</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.765701466165034</v>
+        <v>-1.732909752348121</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.426302383676202</v>
+        <v>-1.434404344543481</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.421854002501462</v>
+        <v>-4.292474369174663</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.575398364764858</v>
+        <v>-3.514081897350387</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.090505062580242</v>
+        <v>-5.040944527277659</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.314643418864321</v>
+        <v>-5.286965752946408</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.486707102771945</v>
+        <v>-4.569411725440354</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.649994781760768</v>
+        <v>-3.80139403018336</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.059086455884589</v>
+        <v>-3.189015989969512</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.996358576855904</v>
+        <v>-3.103753661693574</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.609592521973454</v>
+        <v>-2.788413589749148</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.635795608205811</v>
+        <v>-2.860116982254389</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.663789598774123</v>
+        <v>-2.865664519207819</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.745243491031246</v>
+        <v>-3.915320955893755</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005407</t>
+          <t>X &lt; -0.005402</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.364844601962922</v>
+        <v>-1.230912714764628</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.409066409312473</v>
+        <v>-0.4184559479047536</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.370802079781789</v>
+        <v>-3.262082577644847</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.960000320072119</v>
+        <v>-3.020839961819924</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.33565380152946</v>
+        <v>-4.289599125043551</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.37385024169302</v>
+        <v>-4.46224790466561</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.563706014829449</v>
+        <v>-3.632035397009105</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.464779132889113</v>
+        <v>-2.59173412487128</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.854620349814574</v>
+        <v>-1.959810412937841</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.697827736748458</v>
+        <v>-1.780294512147478</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.16976023195447</v>
+        <v>-1.315538638613333</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.858369540618838</v>
+        <v>-2.037750942497041</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.942197523977086</v>
+        <v>-2.098460708525749</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.613322860297643</v>
+        <v>-2.741277607937363</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004281</t>
+          <t>X &lt; -0.004276</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6255401979939137</v>
+        <v>-0.5632932114017066</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2371081523295047</v>
+        <v>0.184277629881116</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.060612804261879</v>
+        <v>-2.015544008623699</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.070934079050566</v>
+        <v>-2.075774035850088</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.03602466714559</v>
+        <v>-3.040308347904663</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.357335098902304</v>
+        <v>-2.387294692203604</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.870072150256171</v>
+        <v>-1.877608576105871</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.002536408914224</v>
+        <v>-1.056327488732421</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5868741421767467</v>
+        <v>-0.6175627049101351</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8648196305943046</v>
+        <v>-0.8705064141742085</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6351740100247909</v>
+        <v>-0.6940569473430358</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.216240202471404</v>
+        <v>-1.301922560120865</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.158836136969157</v>
+        <v>-1.221343093725601</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.174743275663353</v>
+        <v>-2.209215453403857</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003156</t>
+          <t>X &lt; -0.003151</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3752182600967018</v>
+        <v>-0.3290418660392476</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4174530732265893</v>
+        <v>-0.4689067024645794</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.720564672680226</v>
+        <v>-1.76874024267385</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.133507868897084</v>
+        <v>-1.144622264062136</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.87591393109463</v>
+        <v>-1.880988373712569</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.413113929581954</v>
+        <v>-1.443458209094629</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.001546373215376</v>
+        <v>-1.009880360923056</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3933461997978185</v>
+        <v>-0.442222286840142</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2889023844430056</v>
+        <v>-0.3515893901666729</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8906822229564852</v>
+        <v>-0.927893218506405</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7185873864971626</v>
+        <v>-0.8020006627421594</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7210390952719976</v>
+        <v>-0.8263421762023526</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9754898657353692</v>
+        <v>-1.056483601116007</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.909654795459126</v>
+        <v>-1.962554250651806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.00203</t>
+          <t>X &lt; -0.002026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9184160305343525</v>
+        <v>-0.9520381704960457</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3278975781436415</v>
+        <v>-0.3016517732604171</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.36187350835322</v>
+        <v>-1.333235261220757</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.33603713519841</v>
+        <v>-1.345094664371771</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.263358970492135</v>
+        <v>-2.259574138420788</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.539242408851351</v>
+        <v>-1.561558286504763</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.339457746780404</v>
+        <v>-1.338727486998835</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.095288837224317</v>
+        <v>-1.128464123210904</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4450334404042806</v>
+        <v>-0.4883809259561644</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.152704726065579</v>
+        <v>-1.170264865181359</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.389500162533544</v>
+        <v>-1.445377633512344</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9599115793806092</v>
+        <v>-1.032349292172995</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.166387219018809</v>
+        <v>-1.214590256352153</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.222702850843554</v>
+        <v>-2.243047168644807</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.000904</t>
+          <t>X &lt; -0.0009007</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8445523941707194</v>
+        <v>-0.877705537099807</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.001193032689095</v>
+        <v>-1.038237488385242</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.909553920724349</v>
+        <v>-1.976440086500311</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.747425063793983</v>
+        <v>-1.78605997753003</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.496637978577006</v>
+        <v>-2.517293389504339</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.895681678146531</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.433943949981007</v>
+        <v>-1.458219011332531</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8688328730634396</v>
+        <v>-0.9233398809427626</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5047998504726721</v>
+        <v>-0.5640818689723943</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.294002192643454</v>
+        <v>-1.32734109787944</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.769197736291567</v>
+        <v>-1.8343283049552</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.093788734534364</v>
+        <v>-1.170468048510962</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.209988220066606</v>
+        <v>-1.262779215535112</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.83531639962731</v>
+        <v>-1.768134808707615</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002218</t>
+          <t>X &lt; 0.0002245</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1863</v>
+        <v>1870</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.304445442299063</v>
+        <v>-1.282790586893391</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.525257203812089</v>
+        <v>-1.503860186070597</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.052416579514272</v>
+        <v>-2.111159306259303</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.268853932216672</v>
+        <v>-2.248226679887125</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.779244291722357</v>
+        <v>-2.737475820839045</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.132397757464481</v>
+        <v>-2.144348604209114</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.895564708370522</v>
+        <v>-1.884662995623579</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.422801336318592</v>
+        <v>-1.467616696406026</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.215686978096059</v>
+        <v>-1.262134747214404</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.851128562629668</v>
+        <v>-1.872173910605547</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.455932126854727</v>
+        <v>-2.50389319298931</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.694871734630617</v>
+        <v>-1.750910848996945</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.792961396317615</v>
+        <v>-1.825384649425011</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.050317533530702</v>
+        <v>-2.081860298903685</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001348</t>
+          <t>X &lt; 0.00135</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.048318566936423</v>
+        <v>-1.056078053780041</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.366538213823752</v>
+        <v>-1.395025184092582</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.783535473562438</v>
+        <v>-1.835689498075979</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.004813933908785</v>
+        <v>-2.034289736542206</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.283173211978195</v>
+        <v>-2.288907249150618</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.631462193310206</v>
+        <v>-1.687637450650797</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.716172552576374</v>
+        <v>-1.748293539876258</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.593054619964192</v>
+        <v>-1.672865281936296</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.277211529195405</v>
+        <v>-1.35595004229576</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.569163310757531</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.929412485897323</v>
+        <v>-1.96118539286384</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.633678589781283</v>
+        <v>-1.668166612286171</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.25232072079389</v>
+        <v>-1.285862742037622</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.780946220968104</v>
+        <v>-1.810106001595578</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002473</t>
+          <t>X &lt; 0.002475</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2412</v>
+        <v>2419</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5602221024054828</v>
+        <v>-0.5925860516911143</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7036723715320647</v>
+        <v>-0.7517047516269955</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.159052094545856</v>
+        <v>-1.227950990766786</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.337624377998935</v>
+        <v>-1.386845827439885</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.564362824769951</v>
+        <v>-1.587316090504025</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.244914881602945</v>
+        <v>-1.314530571685097</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.081280870008193</v>
+        <v>-1.127661908435307</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.029260075543377</v>
+        <v>-1.076158061034882</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.8832028945920456</v>
+        <v>-0.925672397146144</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9877800760150635</v>
+        <v>-1.006313529571372</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.169667454752421</v>
+        <v>-1.169165785530247</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.195340990110473</v>
+        <v>-1.212198605711478</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8695324567682619</v>
+        <v>-0.8821934448276636</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.159642086290248</v>
+        <v>-1.188907229066636</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003599</t>
+          <t>X &lt; 0.0036</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2713</v>
+        <v>2721</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4794470624844038</v>
+        <v>-0.5115786382349867</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.712234379292525</v>
+        <v>-0.7550644052739415</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8301296641782798</v>
+        <v>-0.8920158932218101</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8272366000589741</v>
+        <v>-0.8721832093072024</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.419395439008028</v>
+        <v>-1.434799921792511</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.139138575495515</v>
+        <v>-1.198698188740266</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.223848934761683</v>
+        <v>-1.259354277965727</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.045551945382158</v>
+        <v>-1.081746705031449</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6079686413210368</v>
+        <v>-0.6583601553489089</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8319669663695919</v>
+        <v>-0.858106504152147</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.163655867952897</v>
+        <v>-1.172379110278541</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9615911683851763</v>
+        <v>-0.9838441548247445</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9764362000331488</v>
+        <v>-0.9913742246383208</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.098774902367133</v>
+        <v>-1.126191672828412</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2956</v>
+        <v>2965</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4418192998299375</v>
+        <v>-0.4737604280509089</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5856961896804478</v>
+        <v>-0.6252754420293698</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9961483818776742</v>
+        <v>-1.052683464014109</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.084043776370798</v>
+        <v>-1.124819624819629</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.165609534465347</v>
+        <v>-1.176358328061113</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9176179057811638</v>
+        <v>-0.970912876582247</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.288150640602069</v>
+        <v>-1.334599268838012</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.061505053440534</v>
+        <v>-1.108852486176666</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.7662561055909407</v>
+        <v>-0.8243994744095957</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.9064756792104305</v>
+        <v>-0.9406808854132578</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.126337835386465</v>
+        <v>-1.144821332949348</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9042225821968586</v>
+        <v>-0.9332942263113111</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9523747882326177</v>
+        <v>-0.9726957213165761</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.046091660700554</v>
+        <v>-1.075917526271098</v>
       </c>
     </row>
     <row r="27">
@@ -5000,205 +5000,205 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3184</v>
+        <v>3194</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1655217877308459</v>
+        <v>-0.2302867155802986</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2266874131130407</v>
+        <v>-0.2976000628076036</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6045942347151509</v>
+        <v>-0.6288575762706969</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8959530938597595</v>
+        <v>-0.936336859017274</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7595995719958921</v>
+        <v>-0.7695410140272969</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3825842580154983</v>
+        <v>-0.4030347829309591</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.795126912068433</v>
+        <v>-0.8217625685013132</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5867840954175989</v>
+        <v>-0.6143185236330169</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3169749850658903</v>
+        <v>-0.3528277879276445</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1769680361611279</v>
+        <v>-0.2211404975664948</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3327416125606959</v>
+        <v>-0.3627222963693981</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.09241928331687888</v>
+        <v>-0.1306499536634504</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4497757881216558</v>
+        <v>-0.4769890319407892</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.6460875807609483</v>
+        <v>-0.6800340136562824</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.006977</t>
+          <t>X &lt; 0.006976</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3402</v>
+        <v>3412</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.008832065540630651</v>
+        <v>-0.05397147400979208</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2098870635337136</v>
+        <v>-0.2763833821106871</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6474831214833543</v>
+        <v>-0.6701213704253917</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7946430877200044</v>
+        <v>-0.8327205114277447</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9066681231391414</v>
+        <v>-0.9124931972758219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5641229964683561</v>
+        <v>-0.5812110420134999</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8090348108719212</v>
+        <v>-0.8308687709588938</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6145615587277433</v>
+        <v>-0.6371161073452924</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3365728458046746</v>
+        <v>-0.3654051745554057</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3480558852470139</v>
+        <v>-0.382565625717838</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5070131575028398</v>
+        <v>-0.5281409195204034</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3093208905883387</v>
+        <v>-0.3365128769279622</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.611928399793598</v>
+        <v>-0.6274310269456151</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.6636651806947711</v>
+        <v>-0.6844018164165817</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.008103</t>
+          <t>X &lt; 0.008101</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3558</v>
+        <v>3569</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.05862535565336202</v>
+        <v>-0.09323560247849372</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3386007230379562</v>
+        <v>-0.3761284852245055</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7463299387258786</v>
+        <v>-0.7828054837643066</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8532851360653027</v>
+        <v>-0.8765725468269494</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9560537014321824</v>
+        <v>-0.9744322552935429</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5594259185115007</v>
+        <v>-0.5618647963012933</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5167763512784447</v>
+        <v>-0.5235243134677603</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4074798160819668</v>
+        <v>-0.4147806435699692</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1443693924545286</v>
+        <v>-0.156653836174776</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2769760170675681</v>
+        <v>-0.2933902216072184</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4379301189314972</v>
+        <v>-0.4539507401687146</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2193308949796986</v>
+        <v>-0.2401662245270941</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.483254932908153</v>
+        <v>-0.5076303964678175</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5227898102897086</v>
+        <v>-0.5511060170080384</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.009228</t>
+          <t>X &lt; 0.009226</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3705</v>
+        <v>3716</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.03336358298190589</v>
+        <v>-0.05505413773914114</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1507515720781427</v>
+        <v>-0.174877745254868</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6655602683101662</v>
+        <v>-0.6883691802367409</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7631086608617679</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8830908527016916</v>
+        <v>-0.8990235770421506</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5442377368653837</v>
+        <v>-0.5456795190180657</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5605070061123172</v>
+        <v>-0.5649636160436131</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3662655536335393</v>
+        <v>-0.3714548130329689</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1159854251596428</v>
+        <v>-0.1249744147750107</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1422066373367272</v>
+        <v>-0.1544449059332038</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2778899862099706</v>
+        <v>-0.2898016880719112</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1205048052557345</v>
+        <v>-0.1359181042093525</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3905989769596445</v>
+        <v>-0.4084042653374027</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4465744957678268</v>
+        <v>-0.4671921202514611</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3814</v>
+        <v>3825</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.09000931509144294</v>
+        <v>-0.1117802294751016</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3022432631695438</v>
+        <v>-0.3253619217768673</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6306643580264222</v>
+        <v>-0.6529110924107471</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6955604986560644</v>
+        <v>-0.7176959487160346</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6443493748315205</v>
+        <v>-0.6590713615176824</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3327810520140559</v>
+        <v>-0.3341073923987352</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4032896884756667</v>
+        <v>-0.406705157227826</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.358766975048006</v>
+        <v>-0.3624289232464335</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.0911839113780033</v>
+        <v>-0.09790344715983679</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.03614745858884305</v>
+        <v>-0.04551391241177782</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1737739256293409</v>
+        <v>-0.1828008117225792</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.09849137833776211</v>
+        <v>-0.1100058443721537</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1893808750399799</v>
+        <v>-0.2030213599624702</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.237252635188824</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3913</v>
+        <v>3924</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1630352358323677</v>
+        <v>-0.1727134509032524</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2322295121332161</v>
+        <v>-0.2432253776413091</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5113383401575007</v>
+        <v>-0.5215973101521456</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6222614160011588</v>
+        <v>-0.6322509171479496</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5349175201043082</v>
+        <v>-0.5367047364624327</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3256944671594084</v>
+        <v>-0.3264040377702599</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4220701658589761</v>
+        <v>-0.4241379182850835</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2628922661188966</v>
+        <v>-0.2654897309202724</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.04745953617026544</v>
+        <v>0.04236703270901643</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.07965914284881848</v>
+        <v>0.07270836914726431</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0851697214923206</v>
+        <v>-0.09169854009292067</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.03644169039347389</v>
+        <v>-0.04472045824859094</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.01765225066196052</v>
+        <v>0.007525984555933007</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.002311583473208145</v>
+        <v>-0.009354343505115992</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01261</t>
+          <t>X &lt; 0.0126</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3987</v>
+        <v>3998</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1559160305343497</v>
+        <v>-0.1659721740141578</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2536425086944618</v>
+        <v>-0.2644039013124839</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4348474953467161</v>
+        <v>-0.4451107306928677</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5162680795509544</v>
+        <v>-0.5263467503297861</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4655084884311194</v>
+        <v>-0.4665567098492076</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2796665165108223</v>
+        <v>-0.2800468187666141</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3257394452883275</v>
+        <v>-0.3271464636324026</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1781432919796018</v>
+        <v>-0.180015408804735</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.05000440651858185</v>
+        <v>-0.05338070344738099</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.0341852122091808</v>
+        <v>-0.03885753832668826</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1496567818398304</v>
+        <v>-0.1540397156851938</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1262800613670336</v>
+        <v>-0.1318702290076388</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.106083801644175</v>
+        <v>-0.1129308812528791</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.09189953493865488</v>
+        <v>-0.09990675528695903</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4044</v>
+        <v>4055</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05301363960509065</v>
+        <v>-0.05190140207479033</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2212934450972028</v>
+        <v>-0.2206555193371571</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3068488474407687</v>
+        <v>-0.3060136174918213</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3852620796143924</v>
+        <v>-0.3842031277455646</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3674274318008486</v>
+        <v>-0.3680455414018624</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3033881725295089</v>
+        <v>-0.3033628169573674</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3253253459858385</v>
+        <v>-0.3260400180335594</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2851453604141696</v>
+        <v>-0.2860101281951657</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2337876311550602</v>
+        <v>-0.2355901055091394</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.180797203814798</v>
+        <v>-0.1836114732587077</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2234327711087687</v>
+        <v>-0.2261508155593219</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1752035282365654</v>
+        <v>-0.1788445943021841</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1859463807287653</v>
+        <v>-0.1903910747036122</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1440720630139438</v>
+        <v>-0.1494074612502985</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01486</t>
+          <t>X &lt; 0.01485</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0661084796640381</v>
+        <v>-0.06512404982586162</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1686102158002427</v>
+        <v>-0.1681238330068808</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2312934249585723</v>
+        <v>-0.2306668200796551</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3085620055891951</v>
+        <v>-0.307717851025906</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3182508012961378</v>
+        <v>-0.3187365893821053</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2283935396736751</v>
+        <v>-0.2284412405977605</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2015475104427793</v>
+        <v>-0.2023330876002376</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1886356221231651</v>
+        <v>-0.1894903815420079</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1624252688770582</v>
+        <v>-0.1640155127397307</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1142978981850646</v>
+        <v>-0.1167406746805923</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1332173051683014</v>
+        <v>-0.1356252016666417</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06045868877727401</v>
+        <v>-0.06372239865704898</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.07338797627772919</v>
+        <v>-0.0773101565523362</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.03049115297518767</v>
+        <v>-0.03517608237140024</v>
       </c>
     </row>
   </sheetData>
